--- a/research/traditional_assets/database/data/chile/chile_computer_services.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_computer_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09997794831377771</v>
+        <v>0.09974085785333053</v>
       </c>
       <c r="C2">
-        <v>641.2387603757157</v>
+        <v>635.9745429825944</v>
       </c>
       <c r="D2">
-        <v>499.3387603757158</v>
+        <v>501.5335429825943</v>
       </c>
       <c r="E2">
-        <v>-424.5</v>
+        <v>-417.041</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.459</v>
       </c>
       <c r="G2">
         <v>141.9</v>
@@ -1451,28 +1451,28 @@
         <v>125.725</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3751877</v>
       </c>
       <c r="N2">
-        <v>125.725</v>
+        <v>125.3498123</v>
       </c>
       <c r="O2">
-        <v>33.94575</v>
+        <v>33.844449321</v>
       </c>
       <c r="P2">
-        <v>91.77924999999999</v>
+        <v>91.505362979</v>
       </c>
       <c r="Q2">
-        <v>114.67925</v>
+        <v>114.405362979</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09997794831377771</v>
+        <v>0.1003774422760914</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763957</v>
+        <v>0.9996050220926561</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>335.0989384779938</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09974085785333053</v>
+        <v>0.09950376739288333</v>
       </c>
       <c r="C3">
-        <v>635.9745429825944</v>
+        <v>630.7297045658134</v>
       </c>
       <c r="D3">
-        <v>501.5335429825943</v>
+        <v>503.7477045658135</v>
       </c>
       <c r="E3">
-        <v>-417.041</v>
+        <v>-409.582</v>
       </c>
       <c r="F3">
-        <v>7.459</v>
+        <v>14.918</v>
       </c>
       <c r="G3">
         <v>141.9</v>
@@ -1533,28 +1533,28 @@
         <v>125.725</v>
       </c>
       <c r="M3">
-        <v>0.3751877</v>
+        <v>0.7503753999999999</v>
       </c>
       <c r="N3">
-        <v>125.3498123</v>
+        <v>124.9746246</v>
       </c>
       <c r="O3">
-        <v>33.844449321</v>
+        <v>33.743148642</v>
       </c>
       <c r="P3">
-        <v>91.505362979</v>
+        <v>91.231475958</v>
       </c>
       <c r="Q3">
-        <v>114.405362979</v>
+        <v>114.131475958</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1003774422760914</v>
+        <v>0.1007850891764116</v>
       </c>
       <c r="T3">
-        <v>0.9996050220926561</v>
+        <v>1.007071218231697</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>335.0989384779938</v>
+        <v>167.5494692389969</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09950376739288333</v>
+        <v>0.09926667693243611</v>
       </c>
       <c r="C4">
-        <v>630.7297045658134</v>
+        <v>625.5045029254097</v>
       </c>
       <c r="D4">
-        <v>503.7477045658135</v>
+        <v>505.9815029254097</v>
       </c>
       <c r="E4">
-        <v>-409.582</v>
+        <v>-402.123</v>
       </c>
       <c r="F4">
-        <v>14.918</v>
+        <v>22.377</v>
       </c>
       <c r="G4">
         <v>141.9</v>
@@ -1615,28 +1615,28 @@
         <v>125.725</v>
       </c>
       <c r="M4">
-        <v>0.7503753999999999</v>
+        <v>1.1255631</v>
       </c>
       <c r="N4">
-        <v>124.9746246</v>
+        <v>124.5994369</v>
       </c>
       <c r="O4">
-        <v>33.743148642</v>
+        <v>33.641847963</v>
       </c>
       <c r="P4">
-        <v>91.231475958</v>
+        <v>90.957588937</v>
       </c>
       <c r="Q4">
-        <v>114.131475958</v>
+        <v>113.857588937</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1007850891764116</v>
+        <v>0.1012011411674599</v>
       </c>
       <c r="T4">
-        <v>1.007071218231697</v>
+        <v>1.014691356559172</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>167.5494692389969</v>
+        <v>111.6996461593313</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09926667693243611</v>
+        <v>0.09902958647198891</v>
       </c>
       <c r="C5">
-        <v>625.5045029254097</v>
+        <v>620.2992004544988</v>
       </c>
       <c r="D5">
-        <v>505.9815029254097</v>
+        <v>508.2352004544987</v>
       </c>
       <c r="E5">
-        <v>-402.123</v>
+        <v>-394.664</v>
       </c>
       <c r="F5">
-        <v>22.377</v>
+        <v>29.836</v>
       </c>
       <c r="G5">
         <v>141.9</v>
@@ -1697,28 +1697,28 @@
         <v>125.725</v>
       </c>
       <c r="M5">
-        <v>1.1255631</v>
+        <v>1.5007508</v>
       </c>
       <c r="N5">
-        <v>124.5994369</v>
+        <v>124.2242492</v>
       </c>
       <c r="O5">
-        <v>33.641847963</v>
+        <v>33.540547284</v>
       </c>
       <c r="P5">
-        <v>90.957588937</v>
+        <v>90.68370191599999</v>
       </c>
       <c r="Q5">
-        <v>113.857588937</v>
+        <v>113.583701916</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1012011411674599</v>
+        <v>0.1016258609083218</v>
       </c>
       <c r="T5">
-        <v>1.014691356559172</v>
+        <v>1.02247024776847</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>111.6996461593313</v>
+        <v>83.77473461949846</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09902958647198891</v>
+        <v>0.09879249601154171</v>
       </c>
       <c r="C6">
-        <v>620.2992004544988</v>
+        <v>615.1140642420243</v>
       </c>
       <c r="D6">
-        <v>508.2352004544987</v>
+        <v>510.5090642420242</v>
       </c>
       <c r="E6">
-        <v>-394.664</v>
+        <v>-387.205</v>
       </c>
       <c r="F6">
-        <v>29.836</v>
+        <v>37.295</v>
       </c>
       <c r="G6">
         <v>141.9</v>
@@ -1779,28 +1779,28 @@
         <v>125.725</v>
       </c>
       <c r="M6">
-        <v>1.5007508</v>
+        <v>1.8759385</v>
       </c>
       <c r="N6">
-        <v>124.2242492</v>
+        <v>123.8490615</v>
       </c>
       <c r="O6">
-        <v>33.540547284</v>
+        <v>33.439246605</v>
       </c>
       <c r="P6">
-        <v>90.68370191599999</v>
+        <v>90.40981489499998</v>
       </c>
       <c r="Q6">
-        <v>113.583701916</v>
+        <v>113.309814895</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1016258609083218</v>
+        <v>0.1020595221174123</v>
       </c>
       <c r="T6">
-        <v>1.02247024776847</v>
+        <v>1.030412905108489</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>83.77473461949846</v>
+        <v>67.01978769559877</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09879249601154171</v>
+        <v>0.09855540555109453</v>
       </c>
       <c r="C7">
-        <v>615.1140642420243</v>
+        <v>609.9493661782755</v>
       </c>
       <c r="D7">
-        <v>510.5090642420242</v>
+        <v>512.8033661782755</v>
       </c>
       <c r="E7">
-        <v>-387.205</v>
+        <v>-379.746</v>
       </c>
       <c r="F7">
-        <v>37.295</v>
+        <v>44.754</v>
       </c>
       <c r="G7">
         <v>141.9</v>
@@ -1861,28 +1861,28 @@
         <v>125.725</v>
       </c>
       <c r="M7">
-        <v>1.8759385</v>
+        <v>2.2511262</v>
       </c>
       <c r="N7">
-        <v>123.8490615</v>
+        <v>123.4738738</v>
       </c>
       <c r="O7">
-        <v>33.439246605</v>
+        <v>33.337945926</v>
       </c>
       <c r="P7">
-        <v>90.40981489499998</v>
+        <v>90.13592787399999</v>
       </c>
       <c r="Q7">
-        <v>113.309814895</v>
+        <v>113.035927874</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1020595221174123</v>
+        <v>0.1025024101607389</v>
       </c>
       <c r="T7">
-        <v>1.030412905108489</v>
+        <v>1.03852455515787</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>67.01978769559877</v>
+        <v>55.84982307966563</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09855540555109453</v>
+        <v>0.09831831509064733</v>
       </c>
       <c r="C8">
-        <v>609.9493661782755</v>
+        <v>604.8053830632658</v>
       </c>
       <c r="D8">
-        <v>512.8033661782755</v>
+        <v>515.1183830632658</v>
       </c>
       <c r="E8">
-        <v>-379.746</v>
+        <v>-372.287</v>
       </c>
       <c r="F8">
-        <v>44.754</v>
+        <v>52.21299999999999</v>
       </c>
       <c r="G8">
         <v>141.9</v>
@@ -1943,28 +1943,28 @@
         <v>125.725</v>
       </c>
       <c r="M8">
-        <v>2.2511262</v>
+        <v>2.6263139</v>
       </c>
       <c r="N8">
-        <v>123.4738738</v>
+        <v>123.0986861</v>
       </c>
       <c r="O8">
-        <v>33.337945926</v>
+        <v>33.236645247</v>
       </c>
       <c r="P8">
-        <v>90.13592787399999</v>
+        <v>89.862040853</v>
       </c>
       <c r="Q8">
-        <v>113.035927874</v>
+        <v>112.762040853</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1025024101607389</v>
+        <v>0.1029548226781154</v>
       </c>
       <c r="T8">
-        <v>1.03852455515787</v>
+        <v>1.046810649294335</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>55.84982307966563</v>
+        <v>47.87127692542769</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09831831509064731</v>
+        <v>0.09808122463020011</v>
       </c>
       <c r="C9">
-        <v>604.8053830632659</v>
+        <v>599.6823967180558</v>
       </c>
       <c r="D9">
-        <v>515.1183830632659</v>
+        <v>517.4543967180558</v>
       </c>
       <c r="E9">
-        <v>-372.287</v>
+        <v>-364.828</v>
       </c>
       <c r="F9">
-        <v>52.213</v>
+        <v>59.672</v>
       </c>
       <c r="G9">
         <v>141.9</v>
@@ -2025,28 +2025,28 @@
         <v>125.725</v>
       </c>
       <c r="M9">
-        <v>2.6263139</v>
+        <v>3.0015016</v>
       </c>
       <c r="N9">
-        <v>123.0986861</v>
+        <v>122.7234984</v>
       </c>
       <c r="O9">
-        <v>33.236645247</v>
+        <v>33.135344568</v>
       </c>
       <c r="P9">
-        <v>89.862040853</v>
+        <v>89.58815383199999</v>
       </c>
       <c r="Q9">
-        <v>112.762040853</v>
+        <v>112.488153832</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1029548226781154</v>
+        <v>0.1034170702502175</v>
       </c>
       <c r="T9">
-        <v>1.046810649294335</v>
+        <v>1.055276875912028</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.87127692542769</v>
+        <v>41.88736730974923</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09808122463020011</v>
+        <v>0.09784413416975293</v>
       </c>
       <c r="C10">
-        <v>599.6823967180558</v>
+        <v>594.5806940991237</v>
       </c>
       <c r="D10">
-        <v>517.4543967180558</v>
+        <v>519.8116940991237</v>
       </c>
       <c r="E10">
-        <v>-364.828</v>
+        <v>-357.369</v>
       </c>
       <c r="F10">
-        <v>59.672</v>
+        <v>67.131</v>
       </c>
       <c r="G10">
         <v>141.9</v>
@@ -2107,28 +2107,28 @@
         <v>125.725</v>
       </c>
       <c r="M10">
-        <v>3.0015016</v>
+        <v>3.3766893</v>
       </c>
       <c r="N10">
-        <v>122.7234984</v>
+        <v>122.3483107</v>
       </c>
       <c r="O10">
-        <v>33.135344568</v>
+        <v>33.034043889</v>
       </c>
       <c r="P10">
-        <v>89.58815383199999</v>
+        <v>89.314266811</v>
       </c>
       <c r="Q10">
-        <v>112.488153832</v>
+        <v>112.214266811</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1034170702502175</v>
+        <v>0.1038894771096186</v>
       </c>
       <c r="T10">
-        <v>1.055276875912028</v>
+        <v>1.063929173444395</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.88736730974923</v>
+        <v>37.23321538644376</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09784413416975293</v>
+        <v>0.09760704370930573</v>
       </c>
       <c r="C11">
-        <v>594.5806940991237</v>
+        <v>589.5005674158742</v>
       </c>
       <c r="D11">
-        <v>519.8116940991237</v>
+        <v>522.1905674158743</v>
       </c>
       <c r="E11">
-        <v>-357.369</v>
+        <v>-349.91</v>
       </c>
       <c r="F11">
-        <v>67.131</v>
+        <v>74.58999999999999</v>
       </c>
       <c r="G11">
         <v>141.9</v>
@@ -2189,28 +2189,28 @@
         <v>125.725</v>
       </c>
       <c r="M11">
-        <v>3.3766893</v>
+        <v>3.751876999999999</v>
       </c>
       <c r="N11">
-        <v>122.3483107</v>
+        <v>121.973123</v>
       </c>
       <c r="O11">
-        <v>33.034043889</v>
+        <v>32.93274321000001</v>
       </c>
       <c r="P11">
-        <v>89.314266811</v>
+        <v>89.04037979</v>
       </c>
       <c r="Q11">
-        <v>112.214266811</v>
+        <v>111.94037979</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1038894771096186</v>
+        <v>0.1043723818992286</v>
       </c>
       <c r="T11">
-        <v>1.063929173444395</v>
+        <v>1.072773744255259</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.23321538644376</v>
+        <v>33.50989384779939</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09760704370930573</v>
+        <v>0.09736995324885851</v>
       </c>
       <c r="C12">
-        <v>589.5005674158742</v>
+        <v>584.4423142513887</v>
       </c>
       <c r="D12">
-        <v>522.1905674158743</v>
+        <v>524.5913142513887</v>
       </c>
       <c r="E12">
-        <v>-349.91</v>
+        <v>-342.451</v>
       </c>
       <c r="F12">
-        <v>74.59</v>
+        <v>82.04899999999999</v>
       </c>
       <c r="G12">
         <v>141.9</v>
@@ -2271,28 +2271,28 @@
         <v>125.725</v>
       </c>
       <c r="M12">
-        <v>3.751877</v>
+        <v>4.127064699999999</v>
       </c>
       <c r="N12">
-        <v>121.973123</v>
+        <v>121.5979353</v>
       </c>
       <c r="O12">
-        <v>32.93274321000001</v>
+        <v>32.831442531</v>
       </c>
       <c r="P12">
-        <v>89.04037979</v>
+        <v>88.766492769</v>
       </c>
       <c r="Q12">
-        <v>111.94037979</v>
+        <v>111.666492769</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1043723818992286</v>
+        <v>0.1048661384818635</v>
       </c>
       <c r="T12">
-        <v>1.072773744255259</v>
+        <v>1.081817069466367</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.50989384779938</v>
+        <v>30.46353986163581</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09736995324885851</v>
+        <v>0.09713286278841132</v>
       </c>
       <c r="C13">
-        <v>584.4423142513887</v>
+        <v>579.4062376865206</v>
       </c>
       <c r="D13">
-        <v>524.5913142513887</v>
+        <v>527.0142376865207</v>
       </c>
       <c r="E13">
-        <v>-342.451</v>
+        <v>-334.992</v>
       </c>
       <c r="F13">
-        <v>82.04899999999999</v>
+        <v>89.508</v>
       </c>
       <c r="G13">
         <v>141.9</v>
@@ -2353,28 +2353,28 @@
         <v>125.725</v>
       </c>
       <c r="M13">
-        <v>4.127064699999999</v>
+        <v>4.5022524</v>
       </c>
       <c r="N13">
-        <v>121.5979353</v>
+        <v>121.2227476</v>
       </c>
       <c r="O13">
-        <v>32.831442531</v>
+        <v>32.730141852</v>
       </c>
       <c r="P13">
-        <v>88.766492769</v>
+        <v>88.49260574799999</v>
       </c>
       <c r="Q13">
-        <v>111.666492769</v>
+        <v>111.392605748</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1048661384818635</v>
+        <v>0.1053711168050129</v>
       </c>
       <c r="T13">
-        <v>1.081817069466367</v>
+        <v>1.09106592479591</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.46353986163581</v>
+        <v>27.92491153983282</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09713286278841132</v>
+        <v>0.09689577232796413</v>
       </c>
       <c r="C14">
-        <v>579.4062376865206</v>
+        <v>574.3926464274497</v>
       </c>
       <c r="D14">
-        <v>527.0142376865207</v>
+        <v>529.4596464274497</v>
       </c>
       <c r="E14">
-        <v>-334.992</v>
+        <v>-327.533</v>
       </c>
       <c r="F14">
-        <v>89.508</v>
+        <v>96.967</v>
       </c>
       <c r="G14">
         <v>141.9</v>
@@ -2435,28 +2435,28 @@
         <v>125.725</v>
       </c>
       <c r="M14">
-        <v>4.5022524</v>
+        <v>4.877440099999999</v>
       </c>
       <c r="N14">
-        <v>121.2227476</v>
+        <v>120.8475599</v>
       </c>
       <c r="O14">
-        <v>32.730141852</v>
+        <v>32.628841173</v>
       </c>
       <c r="P14">
-        <v>88.49260574799999</v>
+        <v>88.218718727</v>
       </c>
       <c r="Q14">
-        <v>111.392605748</v>
+        <v>111.118718727</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1053711168050129</v>
+        <v>0.1058877038252461</v>
       </c>
       <c r="T14">
-        <v>1.09106592479591</v>
+        <v>1.10052739748935</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.92491153983282</v>
+        <v>25.77684142138414</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09689577232796413</v>
+        <v>0.09665868186751693</v>
       </c>
       <c r="C15">
-        <v>574.3926464274497</v>
+        <v>569.4018549367991</v>
       </c>
       <c r="D15">
-        <v>529.4596464274497</v>
+        <v>531.9278549367991</v>
       </c>
       <c r="E15">
-        <v>-327.533</v>
+        <v>-320.074</v>
       </c>
       <c r="F15">
-        <v>96.967</v>
+        <v>104.426</v>
       </c>
       <c r="G15">
         <v>141.9</v>
@@ -2517,28 +2517,28 @@
         <v>125.725</v>
       </c>
       <c r="M15">
-        <v>4.877440099999999</v>
+        <v>5.2526278</v>
       </c>
       <c r="N15">
-        <v>120.8475599</v>
+        <v>120.4723722</v>
       </c>
       <c r="O15">
-        <v>32.628841173</v>
+        <v>32.527540494</v>
       </c>
       <c r="P15">
-        <v>88.218718727</v>
+        <v>87.944831706</v>
       </c>
       <c r="Q15">
-        <v>111.118718727</v>
+        <v>110.844831706</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1058877038252461</v>
+        <v>0.1064163044971127</v>
       </c>
       <c r="T15">
-        <v>1.10052739748935</v>
+        <v>1.110208904431474</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.77684142138414</v>
+        <v>23.93563846271384</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09665868186751693</v>
+        <v>0.09642159140706973</v>
       </c>
       <c r="C16">
-        <v>569.4018549367991</v>
+        <v>564.4341835684399</v>
       </c>
       <c r="D16">
-        <v>531.9278549367991</v>
+        <v>534.41918356844</v>
       </c>
       <c r="E16">
-        <v>-320.074</v>
+        <v>-312.615</v>
       </c>
       <c r="F16">
-        <v>104.426</v>
+        <v>111.885</v>
       </c>
       <c r="G16">
         <v>141.9</v>
@@ -2599,28 +2599,28 @@
         <v>125.725</v>
       </c>
       <c r="M16">
-        <v>5.2526278</v>
+        <v>5.627815500000001</v>
       </c>
       <c r="N16">
-        <v>120.4723722</v>
+        <v>120.0971845</v>
       </c>
       <c r="O16">
-        <v>32.527540494</v>
+        <v>32.426239815</v>
       </c>
       <c r="P16">
-        <v>87.944831706</v>
+        <v>87.67094468499999</v>
       </c>
       <c r="Q16">
-        <v>110.844831706</v>
+        <v>110.570944685</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1064163044971127</v>
+        <v>0.1069573428318467</v>
       </c>
       <c r="T16">
-        <v>1.110208904431474</v>
+        <v>1.120118211536943</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.93563846271384</v>
+        <v>22.33992923186625</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09642159140706973</v>
+        <v>0.09618450094662251</v>
       </c>
       <c r="C17">
-        <v>564.4341835684399</v>
+        <v>559.4899587061018</v>
       </c>
       <c r="D17">
-        <v>534.41918356844</v>
+        <v>536.9339587061019</v>
       </c>
       <c r="E17">
-        <v>-312.615</v>
+        <v>-305.156</v>
       </c>
       <c r="F17">
-        <v>111.885</v>
+        <v>119.344</v>
       </c>
       <c r="G17">
         <v>141.9</v>
@@ -2681,28 +2681,28 @@
         <v>125.725</v>
       </c>
       <c r="M17">
-        <v>5.6278155</v>
+        <v>6.003003199999999</v>
       </c>
       <c r="N17">
-        <v>120.0971845</v>
+        <v>119.7219968</v>
       </c>
       <c r="O17">
-        <v>32.426239815</v>
+        <v>32.324939136</v>
       </c>
       <c r="P17">
-        <v>87.67094468499999</v>
+        <v>87.39705766399999</v>
       </c>
       <c r="Q17">
-        <v>110.570944685</v>
+        <v>110.297057664</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1069573428318467</v>
+        <v>0.1075112630316935</v>
       </c>
       <c r="T17">
-        <v>1.120118211536943</v>
+        <v>1.130263454525875</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.33992923186625</v>
+        <v>20.94368365487462</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09618450094662251</v>
+        <v>0.09594741048617532</v>
       </c>
       <c r="C18">
-        <v>559.4899587061018</v>
+        <v>554.5695129059135</v>
       </c>
       <c r="D18">
-        <v>536.9339587061019</v>
+        <v>539.4725129059135</v>
       </c>
       <c r="E18">
-        <v>-305.156</v>
+        <v>-297.697</v>
       </c>
       <c r="F18">
-        <v>119.344</v>
+        <v>126.803</v>
       </c>
       <c r="G18">
         <v>141.9</v>
@@ -2763,28 +2763,28 @@
         <v>125.725</v>
       </c>
       <c r="M18">
-        <v>6.003003199999999</v>
+        <v>6.3781909</v>
       </c>
       <c r="N18">
-        <v>119.7219968</v>
+        <v>119.3468091</v>
       </c>
       <c r="O18">
-        <v>32.324939136</v>
+        <v>32.223638457</v>
       </c>
       <c r="P18">
-        <v>87.39705766399999</v>
+        <v>87.12317064300001</v>
       </c>
       <c r="Q18">
-        <v>110.297057664</v>
+        <v>110.023170643</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1075112630316935</v>
+        <v>0.1080785307062353</v>
       </c>
       <c r="T18">
-        <v>1.130263454525875</v>
+        <v>1.140653161201288</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.94368365487462</v>
+        <v>19.7117022634114</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09594741048617532</v>
+        <v>0.09571032002572812</v>
       </c>
       <c r="C19">
-        <v>554.5695129059135</v>
+        <v>549.6731850430094</v>
       </c>
       <c r="D19">
-        <v>539.4725129059135</v>
+        <v>542.0351850430095</v>
       </c>
       <c r="E19">
-        <v>-297.697</v>
+        <v>-290.238</v>
       </c>
       <c r="F19">
-        <v>126.803</v>
+        <v>134.262</v>
       </c>
       <c r="G19">
         <v>141.9</v>
@@ -2845,28 +2845,28 @@
         <v>125.725</v>
       </c>
       <c r="M19">
-        <v>6.3781909</v>
+        <v>6.7533786</v>
       </c>
       <c r="N19">
-        <v>119.3468091</v>
+        <v>118.9716214</v>
       </c>
       <c r="O19">
-        <v>32.223638457</v>
+        <v>32.122337778</v>
       </c>
       <c r="P19">
-        <v>87.12317064300001</v>
+        <v>86.84928362199999</v>
       </c>
       <c r="Q19">
-        <v>110.023170643</v>
+        <v>109.749283622</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1080785307062353</v>
+        <v>0.1086596341777172</v>
       </c>
       <c r="T19">
-        <v>1.140653161201288</v>
+        <v>1.151296275356589</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.7117022634114</v>
+        <v>18.61660769322188</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09571032002572812</v>
+        <v>0.09547322956528093</v>
       </c>
       <c r="C20">
-        <v>549.6731850430094</v>
+        <v>544.8013204623309</v>
       </c>
       <c r="D20">
-        <v>542.0351850430095</v>
+        <v>544.6223204623309</v>
       </c>
       <c r="E20">
-        <v>-290.238</v>
+        <v>-282.779</v>
       </c>
       <c r="F20">
-        <v>134.262</v>
+        <v>141.721</v>
       </c>
       <c r="G20">
         <v>141.9</v>
@@ -2927,28 +2927,28 @@
         <v>125.725</v>
       </c>
       <c r="M20">
-        <v>6.7533786</v>
+        <v>7.1285663</v>
       </c>
       <c r="N20">
-        <v>118.9716214</v>
+        <v>118.5964337</v>
       </c>
       <c r="O20">
-        <v>32.122337778</v>
+        <v>32.021037099</v>
       </c>
       <c r="P20">
-        <v>86.84928362199999</v>
+        <v>86.57539660099999</v>
       </c>
       <c r="Q20">
-        <v>109.749283622</v>
+        <v>109.475396601</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1086596341777172</v>
+        <v>0.1092550858830629</v>
       </c>
       <c r="T20">
-        <v>1.151296275356589</v>
+        <v>1.162202182453996</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.61660769322188</v>
+        <v>17.63678623568388</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09547322956528093</v>
+        <v>0.09523613910483374</v>
       </c>
       <c r="C21">
-        <v>544.8013204623309</v>
+        <v>539.9542711337701</v>
       </c>
       <c r="D21">
-        <v>544.6223204623309</v>
+        <v>547.2342711337701</v>
       </c>
       <c r="E21">
-        <v>-282.779</v>
+        <v>-275.32</v>
       </c>
       <c r="F21">
-        <v>141.721</v>
+        <v>149.18</v>
       </c>
       <c r="G21">
         <v>141.9</v>
@@ -3009,28 +3009,28 @@
         <v>125.725</v>
       </c>
       <c r="M21">
-        <v>7.1285663</v>
+        <v>7.503754</v>
       </c>
       <c r="N21">
-        <v>118.5964337</v>
+        <v>118.221246</v>
       </c>
       <c r="O21">
-        <v>32.021037099</v>
+        <v>31.91973642</v>
       </c>
       <c r="P21">
-        <v>86.57539660099999</v>
+        <v>86.30150957999999</v>
       </c>
       <c r="Q21">
-        <v>109.475396601</v>
+        <v>109.20150958</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1092550858830629</v>
+        <v>0.1098654238810422</v>
       </c>
       <c r="T21">
-        <v>1.162202182453996</v>
+        <v>1.173380737228838</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.63678623568388</v>
+        <v>16.75494692389969</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09523613910483374</v>
+        <v>0.09499904864438653</v>
       </c>
       <c r="C22">
-        <v>539.9542711337701</v>
+        <v>535.1323958117977</v>
       </c>
       <c r="D22">
-        <v>547.2342711337701</v>
+        <v>549.8713958117977</v>
       </c>
       <c r="E22">
-        <v>-275.32</v>
+        <v>-267.861</v>
       </c>
       <c r="F22">
-        <v>149.18</v>
+        <v>156.639</v>
       </c>
       <c r="G22">
         <v>141.9</v>
@@ -3091,28 +3091,28 @@
         <v>125.725</v>
       </c>
       <c r="M22">
-        <v>7.503754</v>
+        <v>7.8789417</v>
       </c>
       <c r="N22">
-        <v>118.221246</v>
+        <v>117.8460583</v>
       </c>
       <c r="O22">
-        <v>31.91973642</v>
+        <v>31.818435741</v>
       </c>
       <c r="P22">
-        <v>86.30150957999999</v>
+        <v>86.02762255899999</v>
       </c>
       <c r="Q22">
-        <v>109.20150958</v>
+        <v>108.927622559</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1098654238810422</v>
+        <v>0.110491213473907</v>
       </c>
       <c r="T22">
-        <v>1.173380737228838</v>
+        <v>1.184842293390385</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.75494692389969</v>
+        <v>15.95709230847589</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09499904864438653</v>
+        <v>0.09476195818393933</v>
       </c>
       <c r="C23">
-        <v>535.1323958117977</v>
+        <v>530.3360601997293</v>
       </c>
       <c r="D23">
-        <v>549.8713958117977</v>
+        <v>552.5340601997293</v>
       </c>
       <c r="E23">
-        <v>-267.861</v>
+        <v>-260.402</v>
       </c>
       <c r="F23">
-        <v>156.639</v>
+        <v>164.098</v>
       </c>
       <c r="G23">
         <v>141.9</v>
@@ -3173,28 +3173,28 @@
         <v>125.725</v>
       </c>
       <c r="M23">
-        <v>7.878941699999999</v>
+        <v>8.254129399999998</v>
       </c>
       <c r="N23">
-        <v>117.8460583</v>
+        <v>117.4708706</v>
       </c>
       <c r="O23">
-        <v>31.818435741</v>
+        <v>31.717135062</v>
       </c>
       <c r="P23">
-        <v>86.02762255899999</v>
+        <v>85.753735538</v>
       </c>
       <c r="Q23">
-        <v>108.927622559</v>
+        <v>108.653735538</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.110491213473907</v>
+        <v>0.1111330489537684</v>
       </c>
       <c r="T23">
-        <v>1.184842293390385</v>
+        <v>1.196597735607356</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.9570923084759</v>
+        <v>15.2317699308179</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09476195818393933</v>
+        <v>0.09452486772349213</v>
       </c>
       <c r="C24">
-        <v>530.3360601997293</v>
+        <v>525.5656371187869</v>
       </c>
       <c r="D24">
-        <v>552.5340601997293</v>
+        <v>555.2226371187869</v>
       </c>
       <c r="E24">
-        <v>-260.402</v>
+        <v>-252.943</v>
       </c>
       <c r="F24">
-        <v>164.098</v>
+        <v>171.557</v>
       </c>
       <c r="G24">
         <v>141.9</v>
@@ -3255,28 +3255,28 @@
         <v>125.725</v>
       </c>
       <c r="M24">
-        <v>8.254129399999998</v>
+        <v>8.6293171</v>
       </c>
       <c r="N24">
-        <v>117.4708706</v>
+        <v>117.0956829</v>
       </c>
       <c r="O24">
-        <v>31.717135062</v>
+        <v>31.615834383</v>
       </c>
       <c r="P24">
-        <v>85.753735538</v>
+        <v>85.47984851699999</v>
       </c>
       <c r="Q24">
-        <v>108.653735538</v>
+        <v>108.379848517</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1111330489537684</v>
+        <v>0.1117915554850547</v>
       </c>
       <c r="T24">
-        <v>1.196597735607356</v>
+        <v>1.208658513985807</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.2317699308179</v>
+        <v>14.5695190642606</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09452486772349213</v>
+        <v>0.09428777726304492</v>
       </c>
       <c r="C25">
-        <v>525.5656371187869</v>
+        <v>520.8215066821217</v>
       </c>
       <c r="D25">
-        <v>555.2226371187869</v>
+        <v>557.9375066821218</v>
       </c>
       <c r="E25">
-        <v>-252.943</v>
+        <v>-245.484</v>
       </c>
       <c r="F25">
-        <v>171.557</v>
+        <v>179.016</v>
       </c>
       <c r="G25">
         <v>141.9</v>
@@ -3337,28 +3337,28 @@
         <v>125.725</v>
       </c>
       <c r="M25">
-        <v>8.6293171</v>
+        <v>9.004504800000001</v>
       </c>
       <c r="N25">
-        <v>117.0956829</v>
+        <v>116.7204952</v>
       </c>
       <c r="O25">
-        <v>31.615834383</v>
+        <v>31.514533704</v>
       </c>
       <c r="P25">
-        <v>85.47984851699999</v>
+        <v>85.20596149599999</v>
       </c>
       <c r="Q25">
-        <v>108.379848517</v>
+        <v>108.105961496</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1117915554850547</v>
+        <v>0.1124673911355854</v>
       </c>
       <c r="T25">
-        <v>1.208658513985807</v>
+        <v>1.221036681268954</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.5695190642606</v>
+        <v>13.96245576991641</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09428777726304492</v>
+        <v>0.09405068680259772</v>
       </c>
       <c r="C26">
-        <v>520.8215066821218</v>
+        <v>516.1040564739666</v>
       </c>
       <c r="D26">
-        <v>557.9375066821218</v>
+        <v>560.6790564739666</v>
       </c>
       <c r="E26">
-        <v>-245.484</v>
+        <v>-238.025</v>
       </c>
       <c r="F26">
-        <v>179.016</v>
+        <v>186.475</v>
       </c>
       <c r="G26">
         <v>141.9</v>
@@ -3419,28 +3419,28 @@
         <v>125.725</v>
       </c>
       <c r="M26">
-        <v>9.004504799999999</v>
+        <v>9.379692499999999</v>
       </c>
       <c r="N26">
-        <v>116.7204952</v>
+        <v>116.3453075</v>
       </c>
       <c r="O26">
-        <v>31.514533704</v>
+        <v>31.413233025</v>
       </c>
       <c r="P26">
-        <v>85.20596149599999</v>
+        <v>84.93207447499999</v>
       </c>
       <c r="Q26">
-        <v>108.105961496</v>
+        <v>107.832074475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1124673911355854</v>
+        <v>0.1131612490701303</v>
       </c>
       <c r="T26">
-        <v>1.221036681268954</v>
+        <v>1.233744933012985</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.96245576991641</v>
+        <v>13.40395753911975</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09405068680259772</v>
+        <v>0.09381359634215053</v>
       </c>
       <c r="C27">
-        <v>516.1040564739666</v>
+        <v>511.4136817340955</v>
       </c>
       <c r="D27">
-        <v>560.6790564739666</v>
+        <v>563.4476817340955</v>
       </c>
       <c r="E27">
-        <v>-238.025</v>
+        <v>-230.566</v>
       </c>
       <c r="F27">
-        <v>186.475</v>
+        <v>193.934</v>
       </c>
       <c r="G27">
         <v>141.9</v>
@@ -3501,28 +3501,28 @@
         <v>125.725</v>
       </c>
       <c r="M27">
-        <v>9.379692499999999</v>
+        <v>9.754880199999999</v>
       </c>
       <c r="N27">
-        <v>116.3453075</v>
+        <v>115.9701198</v>
       </c>
       <c r="O27">
-        <v>31.413233025</v>
+        <v>31.311932346</v>
       </c>
       <c r="P27">
-        <v>84.93207447499999</v>
+        <v>84.658187454</v>
       </c>
       <c r="Q27">
-        <v>107.832074475</v>
+        <v>107.558187454</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1131612490701303</v>
+        <v>0.113873859921825</v>
       </c>
       <c r="T27">
-        <v>1.233744933012985</v>
+        <v>1.246796651020369</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.40395753911975</v>
+        <v>12.88842071069207</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09381359634215053</v>
+        <v>0.09387215588170332</v>
       </c>
       <c r="C28">
-        <v>511.4136817340955</v>
+        <v>503.2683127498203</v>
       </c>
       <c r="D28">
-        <v>563.4476817340955</v>
+        <v>562.7613127498204</v>
       </c>
       <c r="E28">
-        <v>-230.566</v>
+        <v>-223.107</v>
       </c>
       <c r="F28">
-        <v>193.934</v>
+        <v>201.393</v>
       </c>
       <c r="G28">
         <v>141.9</v>
@@ -3583,45 +3583,45 @@
         <v>125.725</v>
       </c>
       <c r="M28">
-        <v>9.754880199999999</v>
+        <v>10.4321574</v>
       </c>
       <c r="N28">
-        <v>115.9701198</v>
+        <v>115.2928426</v>
       </c>
       <c r="O28">
-        <v>31.311932346</v>
+        <v>31.129067502</v>
       </c>
       <c r="P28">
-        <v>84.658187454</v>
+        <v>84.163775098</v>
       </c>
       <c r="Q28">
-        <v>107.558187454</v>
+        <v>107.063775098</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.113873859921825</v>
+        <v>0.1146059943584977</v>
       </c>
       <c r="T28">
-        <v>1.246796651020369</v>
+        <v>1.260205950343023</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>12.88842071069207</v>
+        <v>12.05167782456963</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09387215588170332</v>
+        <v>0.09364601542125611</v>
       </c>
       <c r="C29">
-        <v>503.2683127498203</v>
+        <v>498.4691602055937</v>
       </c>
       <c r="D29">
-        <v>562.7613127498204</v>
+        <v>565.4211602055937</v>
       </c>
       <c r="E29">
-        <v>-223.107</v>
+        <v>-215.648</v>
       </c>
       <c r="F29">
-        <v>201.393</v>
+        <v>208.852</v>
       </c>
       <c r="G29">
         <v>141.9</v>
@@ -3665,28 +3665,28 @@
         <v>125.725</v>
       </c>
       <c r="M29">
-        <v>10.4321574</v>
+        <v>10.8185336</v>
       </c>
       <c r="N29">
-        <v>115.2928426</v>
+        <v>114.9064664</v>
       </c>
       <c r="O29">
-        <v>31.129067502</v>
+        <v>31.024745928</v>
       </c>
       <c r="P29">
-        <v>84.163775098</v>
+        <v>83.881720472</v>
       </c>
       <c r="Q29">
-        <v>107.063775098</v>
+        <v>106.781720472</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1146059943584977</v>
+        <v>0.1153584658628557</v>
       </c>
       <c r="T29">
-        <v>1.260205950343023</v>
+        <v>1.273987730202417</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.05167782456963</v>
+        <v>11.62126075940643</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09364601542125611</v>
+        <v>0.09341987496080893</v>
       </c>
       <c r="C30">
-        <v>498.4691602055937</v>
+        <v>493.6952701858426</v>
       </c>
       <c r="D30">
-        <v>565.4211602055937</v>
+        <v>568.1062701858426</v>
       </c>
       <c r="E30">
-        <v>-215.648</v>
+        <v>-208.189</v>
       </c>
       <c r="F30">
-        <v>208.852</v>
+        <v>216.311</v>
       </c>
       <c r="G30">
         <v>141.9</v>
@@ -3747,28 +3747,28 @@
         <v>125.725</v>
       </c>
       <c r="M30">
-        <v>10.8185336</v>
+        <v>11.2049098</v>
       </c>
       <c r="N30">
-        <v>114.9064664</v>
+        <v>114.5200902</v>
       </c>
       <c r="O30">
-        <v>31.024745928</v>
+        <v>30.920424354</v>
       </c>
       <c r="P30">
-        <v>83.881720472</v>
+        <v>83.59966584599999</v>
       </c>
       <c r="Q30">
-        <v>106.781720472</v>
+        <v>106.499665846</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1153584658628557</v>
+        <v>0.1161321337476182</v>
       </c>
       <c r="T30">
-        <v>1.273987730202417</v>
+        <v>1.28815772921278</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.62126075940643</v>
+        <v>11.22052762977173</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09341987496080893</v>
+        <v>0.09319373450036172</v>
       </c>
       <c r="C31">
-        <v>493.6952701858426</v>
+        <v>488.9470043129833</v>
       </c>
       <c r="D31">
-        <v>568.1062701858426</v>
+        <v>570.8170043129833</v>
       </c>
       <c r="E31">
-        <v>-208.189</v>
+        <v>-200.73</v>
       </c>
       <c r="F31">
-        <v>216.311</v>
+        <v>223.77</v>
       </c>
       <c r="G31">
         <v>141.9</v>
@@ -3829,28 +3829,28 @@
         <v>125.725</v>
       </c>
       <c r="M31">
-        <v>11.2049098</v>
+        <v>11.591286</v>
       </c>
       <c r="N31">
-        <v>114.5200902</v>
+        <v>114.133714</v>
       </c>
       <c r="O31">
-        <v>30.920424354</v>
+        <v>30.81610278</v>
       </c>
       <c r="P31">
-        <v>83.59966584599999</v>
+        <v>83.31761122</v>
       </c>
       <c r="Q31">
-        <v>106.499665846</v>
+        <v>106.21761122</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1161321337476182</v>
+        <v>0.1169279064290882</v>
       </c>
       <c r="T31">
-        <v>1.28815772921278</v>
+        <v>1.302732585337725</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.22052762977173</v>
+        <v>10.84651004211267</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09319373450036172</v>
+        <v>0.09296759403991452</v>
       </c>
       <c r="C32">
-        <v>488.9470043129833</v>
+        <v>484.2247311444854</v>
       </c>
       <c r="D32">
-        <v>570.8170043129833</v>
+        <v>573.5537311444854</v>
       </c>
       <c r="E32">
-        <v>-200.73</v>
+        <v>-193.271</v>
       </c>
       <c r="F32">
-        <v>223.77</v>
+        <v>231.229</v>
       </c>
       <c r="G32">
         <v>141.9</v>
@@ -3911,28 +3911,28 @@
         <v>125.725</v>
       </c>
       <c r="M32">
-        <v>11.591286</v>
+        <v>11.9776622</v>
       </c>
       <c r="N32">
-        <v>114.133714</v>
+        <v>113.7473378</v>
       </c>
       <c r="O32">
-        <v>30.81610278</v>
+        <v>30.711781206</v>
       </c>
       <c r="P32">
-        <v>83.31761122</v>
+        <v>83.035556594</v>
       </c>
       <c r="Q32">
-        <v>106.21761122</v>
+        <v>105.935556594</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1169279064290882</v>
+        <v>0.1177467449853834</v>
       </c>
       <c r="T32">
-        <v>1.302732585337725</v>
+        <v>1.317729901060495</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.84651004211267</v>
+        <v>10.49662262139936</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09296759403991452</v>
+        <v>0.09274145357946731</v>
       </c>
       <c r="C33">
-        <v>484.2247311444854</v>
+        <v>479.5288263399217</v>
       </c>
       <c r="D33">
-        <v>573.5537311444854</v>
+        <v>576.3168263399217</v>
       </c>
       <c r="E33">
-        <v>-193.271</v>
+        <v>-185.812</v>
       </c>
       <c r="F33">
-        <v>231.229</v>
+        <v>238.688</v>
       </c>
       <c r="G33">
         <v>141.9</v>
@@ -3993,28 +3993,28 @@
         <v>125.725</v>
       </c>
       <c r="M33">
-        <v>11.9776622</v>
+        <v>12.3640384</v>
       </c>
       <c r="N33">
-        <v>113.7473378</v>
+        <v>113.3609616</v>
       </c>
       <c r="O33">
-        <v>30.711781206</v>
+        <v>30.607459632</v>
       </c>
       <c r="P33">
-        <v>83.035556594</v>
+        <v>82.75350196799999</v>
       </c>
       <c r="Q33">
-        <v>105.935556594</v>
+        <v>105.653501968</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1177467449853834</v>
+        <v>0.1185896670286284</v>
       </c>
       <c r="T33">
-        <v>1.317729901060495</v>
+        <v>1.333168314304522</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.49662262139936</v>
+        <v>10.16860316448063</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09274145357946731</v>
+        <v>0.09251531311902012</v>
       </c>
       <c r="C34">
-        <v>479.5288263399217</v>
+        <v>474.8596728328678</v>
       </c>
       <c r="D34">
-        <v>576.3168263399217</v>
+        <v>579.1066728328678</v>
       </c>
       <c r="E34">
-        <v>-185.812</v>
+        <v>-178.353</v>
       </c>
       <c r="F34">
-        <v>238.688</v>
+        <v>246.147</v>
       </c>
       <c r="G34">
         <v>141.9</v>
@@ -4075,28 +4075,28 @@
         <v>125.725</v>
       </c>
       <c r="M34">
-        <v>12.3640384</v>
+        <v>12.7504146</v>
       </c>
       <c r="N34">
-        <v>113.3609616</v>
+        <v>112.9745854</v>
       </c>
       <c r="O34">
-        <v>30.607459632</v>
+        <v>30.503138058</v>
       </c>
       <c r="P34">
-        <v>82.75350196799999</v>
+        <v>82.47144734199999</v>
       </c>
       <c r="Q34">
-        <v>105.653501968</v>
+        <v>105.371447342</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1185896670286284</v>
+        <v>0.1194577509239106</v>
       </c>
       <c r="T34">
-        <v>1.333168314304522</v>
+        <v>1.349067575705088</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.16860316448063</v>
+        <v>9.860463674647882</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09251531311902012</v>
+        <v>0.09271111265857292</v>
       </c>
       <c r="C35">
-        <v>474.8596728328678</v>
+        <v>464.9835734833407</v>
       </c>
       <c r="D35">
-        <v>579.1066728328678</v>
+        <v>576.6895734833407</v>
       </c>
       <c r="E35">
-        <v>-178.353</v>
+        <v>-170.894</v>
       </c>
       <c r="F35">
-        <v>246.147</v>
+        <v>253.606</v>
       </c>
       <c r="G35">
         <v>141.9</v>
@@ -4157,45 +4157,45 @@
         <v>125.725</v>
       </c>
       <c r="M35">
-        <v>12.7504146</v>
+        <v>13.567921</v>
       </c>
       <c r="N35">
-        <v>112.9745854</v>
+        <v>112.157079</v>
       </c>
       <c r="O35">
-        <v>30.503138058</v>
+        <v>30.28241133</v>
       </c>
       <c r="P35">
-        <v>82.47144734199999</v>
+        <v>81.87466766999999</v>
       </c>
       <c r="Q35">
-        <v>105.371447342</v>
+        <v>104.77466767</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1194577509239106</v>
+        <v>0.1203521403917772</v>
       </c>
       <c r="T35">
-        <v>1.349067575705088</v>
+        <v>1.365448632905671</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>9.860463674647882</v>
+        <v>9.266342278968162</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09271111265857292</v>
+        <v>0.0924973821981257</v>
       </c>
       <c r="C36">
-        <v>464.9835734833407</v>
+        <v>460.1640389581452</v>
       </c>
       <c r="D36">
-        <v>576.6895734833407</v>
+        <v>579.3290389581452</v>
       </c>
       <c r="E36">
-        <v>-170.894</v>
+        <v>-163.435</v>
       </c>
       <c r="F36">
-        <v>253.606</v>
+        <v>261.065</v>
       </c>
       <c r="G36">
         <v>141.9</v>
@@ -4239,28 +4239,28 @@
         <v>125.725</v>
       </c>
       <c r="M36">
-        <v>13.567921</v>
+        <v>13.9669775</v>
       </c>
       <c r="N36">
-        <v>112.157079</v>
+        <v>111.7580225</v>
       </c>
       <c r="O36">
-        <v>30.28241133</v>
+        <v>30.174666075</v>
       </c>
       <c r="P36">
-        <v>81.87466766999999</v>
+        <v>81.58335642499999</v>
       </c>
       <c r="Q36">
-        <v>104.77466767</v>
+        <v>104.483356425</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1203521403917772</v>
+        <v>0.121274049535578</v>
       </c>
       <c r="T36">
-        <v>1.365448632905671</v>
+        <v>1.382333722635502</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.266342278968162</v>
+        <v>9.001589642426215</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0924973821981257</v>
+        <v>0.09228365173767851</v>
       </c>
       <c r="C37">
-        <v>460.1640389581452</v>
+        <v>455.3687768018435</v>
       </c>
       <c r="D37">
-        <v>579.3290389581452</v>
+        <v>581.9927768018435</v>
       </c>
       <c r="E37">
-        <v>-163.435</v>
+        <v>-155.976</v>
       </c>
       <c r="F37">
-        <v>261.065</v>
+        <v>268.524</v>
       </c>
       <c r="G37">
         <v>141.9</v>
@@ -4321,28 +4321,28 @@
         <v>125.725</v>
       </c>
       <c r="M37">
-        <v>13.9669775</v>
+        <v>14.366034</v>
       </c>
       <c r="N37">
-        <v>111.7580225</v>
+        <v>111.358966</v>
       </c>
       <c r="O37">
-        <v>30.174666075</v>
+        <v>30.06692082</v>
       </c>
       <c r="P37">
-        <v>81.58335642499999</v>
+        <v>81.29204518</v>
       </c>
       <c r="Q37">
-        <v>104.483356425</v>
+        <v>104.19204518</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.121274049535578</v>
+        <v>0.1222247683401227</v>
       </c>
       <c r="T37">
-        <v>1.382333722635502</v>
+        <v>1.399746471419391</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.001589642426215</v>
+        <v>8.751545485692155</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09228365173767852</v>
+        <v>0.09206992127723132</v>
       </c>
       <c r="C38">
-        <v>455.3687768018434</v>
+        <v>450.598123371908</v>
       </c>
       <c r="D38">
-        <v>581.9927768018434</v>
+        <v>584.681123371908</v>
       </c>
       <c r="E38">
-        <v>-155.976</v>
+        <v>-148.517</v>
       </c>
       <c r="F38">
-        <v>268.524</v>
+        <v>275.983</v>
       </c>
       <c r="G38">
         <v>141.9</v>
@@ -4403,28 +4403,28 @@
         <v>125.725</v>
       </c>
       <c r="M38">
-        <v>14.366034</v>
+        <v>14.7650905</v>
       </c>
       <c r="N38">
-        <v>111.358966</v>
+        <v>110.9599095</v>
       </c>
       <c r="O38">
-        <v>30.06692082</v>
+        <v>29.959175565</v>
       </c>
       <c r="P38">
-        <v>81.29204518</v>
+        <v>81.000733935</v>
       </c>
       <c r="Q38">
-        <v>104.19204518</v>
+        <v>103.900733935</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1222247683401227</v>
+        <v>0.123205668694018</v>
       </c>
       <c r="T38">
-        <v>1.399746471419391</v>
+        <v>1.417712005878958</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.751545485692155</v>
+        <v>8.515017229322096</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09206992127723132</v>
+        <v>0.09185619081678413</v>
       </c>
       <c r="C39">
-        <v>450.598123371908</v>
+        <v>445.8524212694736</v>
       </c>
       <c r="D39">
-        <v>584.681123371908</v>
+        <v>587.3944212694736</v>
       </c>
       <c r="E39">
-        <v>-148.517</v>
+        <v>-141.058</v>
       </c>
       <c r="F39">
-        <v>275.983</v>
+        <v>283.442</v>
       </c>
       <c r="G39">
         <v>141.9</v>
@@ -4485,28 +4485,28 @@
         <v>125.725</v>
       </c>
       <c r="M39">
-        <v>14.7650905</v>
+        <v>15.164147</v>
       </c>
       <c r="N39">
-        <v>110.9599095</v>
+        <v>110.560853</v>
       </c>
       <c r="O39">
-        <v>29.959175565</v>
+        <v>29.85143031</v>
       </c>
       <c r="P39">
-        <v>81.000733935</v>
+        <v>80.70942269</v>
       </c>
       <c r="Q39">
-        <v>103.900733935</v>
+        <v>103.60942269</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.123205668694018</v>
+        <v>0.1242182109948131</v>
       </c>
       <c r="T39">
-        <v>1.417712005878958</v>
+        <v>1.436257073708189</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.515017229322096</v>
+        <v>8.290937828550462</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09185619081678413</v>
+        <v>0.09164246035633691</v>
       </c>
       <c r="C40">
-        <v>445.8524212694736</v>
+        <v>441.1320194848875</v>
       </c>
       <c r="D40">
-        <v>587.3944212694736</v>
+        <v>590.1330194848875</v>
       </c>
       <c r="E40">
-        <v>-141.058</v>
+        <v>-133.599</v>
       </c>
       <c r="F40">
-        <v>283.442</v>
+        <v>290.901</v>
       </c>
       <c r="G40">
         <v>141.9</v>
@@ -4567,28 +4567,28 @@
         <v>125.725</v>
       </c>
       <c r="M40">
-        <v>15.164147</v>
+        <v>15.5632035</v>
       </c>
       <c r="N40">
-        <v>110.560853</v>
+        <v>110.1617965</v>
       </c>
       <c r="O40">
-        <v>29.85143031</v>
+        <v>29.743685055</v>
       </c>
       <c r="P40">
-        <v>80.70942269</v>
+        <v>80.41811144499999</v>
       </c>
       <c r="Q40">
-        <v>103.60942269</v>
+        <v>103.318111445</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1242182109948131</v>
+        <v>0.125263951403831</v>
       </c>
       <c r="T40">
-        <v>1.436257073708189</v>
+        <v>1.455410176548215</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.290937828550462</v>
+        <v>8.07834967910045</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09164246035633691</v>
+        <v>0.09142872989588972</v>
       </c>
       <c r="C41">
-        <v>441.1320194848875</v>
+        <v>436.4372735473474</v>
       </c>
       <c r="D41">
-        <v>590.1330194848875</v>
+        <v>592.8972735473475</v>
       </c>
       <c r="E41">
-        <v>-133.599</v>
+        <v>-126.14</v>
       </c>
       <c r="F41">
-        <v>290.901</v>
+        <v>298.36</v>
       </c>
       <c r="G41">
         <v>141.9</v>
@@ -4649,28 +4649,28 @@
         <v>125.725</v>
       </c>
       <c r="M41">
-        <v>15.5632035</v>
+        <v>15.96226</v>
       </c>
       <c r="N41">
-        <v>110.1617965</v>
+        <v>109.76274</v>
       </c>
       <c r="O41">
-        <v>29.743685055</v>
+        <v>29.6359398</v>
       </c>
       <c r="P41">
-        <v>80.41811144499999</v>
+        <v>80.12680019999999</v>
       </c>
       <c r="Q41">
-        <v>103.318111445</v>
+        <v>103.0268002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.125263951403831</v>
+        <v>0.1263445498264829</v>
       </c>
       <c r="T41">
-        <v>1.455410176548215</v>
+        <v>1.475201716149575</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.07834967910045</v>
+        <v>7.876390937122938</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09142872989588972</v>
+        <v>0.09121499943544253</v>
       </c>
       <c r="C42">
-        <v>436.4372735473474</v>
+        <v>431.7685456787671</v>
       </c>
       <c r="D42">
-        <v>592.8972735473475</v>
+        <v>595.6875456787672</v>
       </c>
       <c r="E42">
-        <v>-126.14</v>
+        <v>-118.681</v>
       </c>
       <c r="F42">
-        <v>298.36</v>
+        <v>305.819</v>
       </c>
       <c r="G42">
         <v>141.9</v>
@@ -4731,28 +4731,28 @@
         <v>125.725</v>
       </c>
       <c r="M42">
-        <v>15.96226</v>
+        <v>16.3613165</v>
       </c>
       <c r="N42">
-        <v>109.76274</v>
+        <v>109.3636835</v>
       </c>
       <c r="O42">
-        <v>29.6359398</v>
+        <v>29.528194545</v>
       </c>
       <c r="P42">
-        <v>80.12680019999999</v>
+        <v>79.83548895499999</v>
       </c>
       <c r="Q42">
-        <v>103.0268002</v>
+        <v>102.735488955</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1263445498264829</v>
+        <v>0.1274617787041399</v>
       </c>
       <c r="T42">
-        <v>1.475201716149575</v>
+        <v>1.495664155398438</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.876390937122938</v>
+        <v>7.684283841095549</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09121499943544253</v>
+        <v>0.09124654897499533</v>
       </c>
       <c r="C43">
-        <v>431.7685456787671</v>
+        <v>423.8960122376726</v>
       </c>
       <c r="D43">
-        <v>595.6875456787672</v>
+        <v>595.2740122376727</v>
       </c>
       <c r="E43">
-        <v>-118.681</v>
+        <v>-111.222</v>
       </c>
       <c r="F43">
-        <v>305.819</v>
+        <v>313.278</v>
       </c>
       <c r="G43">
         <v>141.9</v>
@@ -4813,45 +4813,45 @@
         <v>125.725</v>
       </c>
       <c r="M43">
-        <v>16.3613165</v>
+        <v>17.0109954</v>
       </c>
       <c r="N43">
-        <v>109.3636835</v>
+        <v>108.7140046</v>
       </c>
       <c r="O43">
-        <v>29.528194545</v>
+        <v>29.352781242</v>
       </c>
       <c r="P43">
-        <v>79.83548895499999</v>
+        <v>79.36122335799999</v>
       </c>
       <c r="Q43">
-        <v>102.735488955</v>
+        <v>102.261223358</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1274617787041399</v>
+        <v>0.1286175327155092</v>
       </c>
       <c r="T43">
-        <v>1.495664155398438</v>
+        <v>1.516832196000711</v>
       </c>
       <c r="U43">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>7.684283841095549</v>
+        <v>7.390807947664249</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09124654897499533</v>
+        <v>0.09103865851454813</v>
       </c>
       <c r="C44">
-        <v>423.8960122376727</v>
+        <v>419.1725440275144</v>
       </c>
       <c r="D44">
-        <v>595.2740122376727</v>
+        <v>598.0095440275144</v>
       </c>
       <c r="E44">
-        <v>-111.222</v>
+        <v>-103.763</v>
       </c>
       <c r="F44">
-        <v>313.278</v>
+        <v>320.737</v>
       </c>
       <c r="G44">
         <v>141.9</v>
@@ -4895,28 +4895,28 @@
         <v>125.725</v>
       </c>
       <c r="M44">
-        <v>17.0109954</v>
+        <v>17.4160191</v>
       </c>
       <c r="N44">
-        <v>108.7140046</v>
+        <v>108.3089809</v>
       </c>
       <c r="O44">
-        <v>29.352781242</v>
+        <v>29.243424843</v>
       </c>
       <c r="P44">
-        <v>79.36122335799999</v>
+        <v>79.06555605699999</v>
       </c>
       <c r="Q44">
-        <v>102.261223358</v>
+        <v>101.965556057</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1286175327155092</v>
+        <v>0.1298138394992072</v>
       </c>
       <c r="T44">
-        <v>1.516832196000711</v>
+        <v>1.53874297486973</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.390807947664251</v>
+        <v>7.218928693067407</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09103865851454813</v>
+        <v>0.09083076805410092</v>
       </c>
       <c r="C45">
-        <v>419.1725440275144</v>
+        <v>414.4743337015955</v>
       </c>
       <c r="D45">
-        <v>598.0095440275144</v>
+        <v>600.7703337015955</v>
       </c>
       <c r="E45">
-        <v>-103.763</v>
+        <v>-96.30400000000003</v>
       </c>
       <c r="F45">
-        <v>320.737</v>
+        <v>328.196</v>
       </c>
       <c r="G45">
         <v>141.9</v>
@@ -4977,28 +4977,28 @@
         <v>125.725</v>
       </c>
       <c r="M45">
-        <v>17.4160191</v>
+        <v>17.8210428</v>
       </c>
       <c r="N45">
-        <v>108.3089809</v>
+        <v>107.9039572</v>
       </c>
       <c r="O45">
-        <v>29.243424843</v>
+        <v>29.134068444</v>
       </c>
       <c r="P45">
-        <v>79.06555605699999</v>
+        <v>78.769888756</v>
       </c>
       <c r="Q45">
-        <v>101.965556057</v>
+        <v>101.669888756</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1298138394992072</v>
+        <v>0.1310528715251802</v>
       </c>
       <c r="T45">
-        <v>1.53874297486973</v>
+        <v>1.5614362815555</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.218928693067407</v>
+        <v>7.054862131861331</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09083076805410092</v>
+        <v>0.09062287759365373</v>
       </c>
       <c r="C46">
-        <v>414.4743337015955</v>
+        <v>409.8017327014206</v>
       </c>
       <c r="D46">
-        <v>600.7703337015955</v>
+        <v>603.5567327014206</v>
       </c>
       <c r="E46">
-        <v>-96.30400000000003</v>
+        <v>-88.84500000000003</v>
       </c>
       <c r="F46">
-        <v>328.196</v>
+        <v>335.655</v>
       </c>
       <c r="G46">
         <v>141.9</v>
@@ -5059,28 +5059,28 @@
         <v>125.725</v>
       </c>
       <c r="M46">
-        <v>17.8210428</v>
+        <v>18.2260665</v>
       </c>
       <c r="N46">
-        <v>107.9039572</v>
+        <v>107.4989335</v>
       </c>
       <c r="O46">
-        <v>29.134068444</v>
+        <v>29.024712045</v>
       </c>
       <c r="P46">
-        <v>78.769888756</v>
+        <v>78.47422145499999</v>
       </c>
       <c r="Q46">
-        <v>101.669888756</v>
+        <v>101.374221455</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1310528715251802</v>
+        <v>0.1323369592611886</v>
       </c>
       <c r="T46">
-        <v>1.5614362815555</v>
+        <v>1.584954799393479</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.054862131861331</v>
+        <v>6.898087417819967</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09062287759365373</v>
+        <v>0.09041498713320653</v>
       </c>
       <c r="C47">
-        <v>409.8017327014206</v>
+        <v>405.1550990188798</v>
       </c>
       <c r="D47">
-        <v>603.5567327014206</v>
+        <v>606.3690990188799</v>
       </c>
       <c r="E47">
-        <v>-88.84500000000003</v>
+        <v>-81.38599999999997</v>
       </c>
       <c r="F47">
-        <v>335.655</v>
+        <v>343.114</v>
       </c>
       <c r="G47">
         <v>141.9</v>
@@ -5141,28 +5141,28 @@
         <v>125.725</v>
       </c>
       <c r="M47">
-        <v>18.2260665</v>
+        <v>18.6310902</v>
       </c>
       <c r="N47">
-        <v>107.4989335</v>
+        <v>107.0939098</v>
       </c>
       <c r="O47">
-        <v>29.024712045</v>
+        <v>28.915355646</v>
       </c>
       <c r="P47">
-        <v>78.47422145499999</v>
+        <v>78.178554154</v>
       </c>
       <c r="Q47">
-        <v>101.374221455</v>
+        <v>101.078554154</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1323369592611886</v>
+        <v>0.1336686058022343</v>
       </c>
       <c r="T47">
-        <v>1.584954799393479</v>
+        <v>1.60934437344768</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.898087417819967</v>
+        <v>6.748128995693444</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09041498713320653</v>
+        <v>0.09020709667275932</v>
       </c>
       <c r="C48">
-        <v>405.1550990188798</v>
+        <v>400.5347973495753</v>
       </c>
       <c r="D48">
-        <v>606.3690990188799</v>
+        <v>609.2077973495753</v>
       </c>
       <c r="E48">
-        <v>-81.38599999999997</v>
+        <v>-73.92699999999996</v>
       </c>
       <c r="F48">
-        <v>343.114</v>
+        <v>350.573</v>
       </c>
       <c r="G48">
         <v>141.9</v>
@@ -5223,28 +5223,28 @@
         <v>125.725</v>
       </c>
       <c r="M48">
-        <v>18.6310902</v>
+        <v>19.0361139</v>
       </c>
       <c r="N48">
-        <v>107.0939098</v>
+        <v>106.6888861</v>
       </c>
       <c r="O48">
-        <v>28.915355646</v>
+        <v>28.805999247</v>
       </c>
       <c r="P48">
-        <v>78.178554154</v>
+        <v>77.88288685299999</v>
       </c>
       <c r="Q48">
-        <v>101.078554154</v>
+        <v>100.782886853</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1336686058022343</v>
+        <v>0.1350505031561497</v>
       </c>
       <c r="T48">
-        <v>1.60934437344768</v>
+        <v>1.634654308786945</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.748128995693444</v>
+        <v>6.604551783019115</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09020709667275932</v>
+        <v>0.08999920621231212</v>
       </c>
       <c r="C49">
-        <v>400.5347973495753</v>
+        <v>395.9411992504751</v>
       </c>
       <c r="D49">
-        <v>609.2077973495753</v>
+        <v>612.0731992504751</v>
       </c>
       <c r="E49">
-        <v>-73.92699999999996</v>
+        <v>-66.46799999999996</v>
       </c>
       <c r="F49">
-        <v>350.573</v>
+        <v>358.032</v>
       </c>
       <c r="G49">
         <v>141.9</v>
@@ -5305,28 +5305,28 @@
         <v>125.725</v>
       </c>
       <c r="M49">
-        <v>19.0361139</v>
+        <v>19.4411376</v>
       </c>
       <c r="N49">
-        <v>106.6888861</v>
+        <v>106.2838624</v>
       </c>
       <c r="O49">
-        <v>28.805999247</v>
+        <v>28.696642848</v>
       </c>
       <c r="P49">
-        <v>77.88288685299999</v>
+        <v>77.58721955199999</v>
       </c>
       <c r="Q49">
-        <v>100.782886853</v>
+        <v>100.487219552</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1350505031561497</v>
+        <v>0.1364855504082925</v>
       </c>
       <c r="T49">
-        <v>1.634654308786945</v>
+        <v>1.660937703177721</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.604551783019115</v>
+        <v>6.466956954206218</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08999920621231212</v>
+        <v>0.08979131575186491</v>
       </c>
       <c r="C50">
-        <v>395.9411992504751</v>
+        <v>391.374683302039</v>
       </c>
       <c r="D50">
-        <v>612.0731992504751</v>
+        <v>614.965683302039</v>
       </c>
       <c r="E50">
-        <v>-66.46800000000002</v>
+        <v>-59.00900000000001</v>
       </c>
       <c r="F50">
-        <v>358.032</v>
+        <v>365.491</v>
       </c>
       <c r="G50">
         <v>141.9</v>
@@ -5387,28 +5387,28 @@
         <v>125.725</v>
       </c>
       <c r="M50">
-        <v>19.4411376</v>
+        <v>19.8461613</v>
       </c>
       <c r="N50">
-        <v>106.2838624</v>
+        <v>105.8788387</v>
       </c>
       <c r="O50">
-        <v>28.696642848</v>
+        <v>28.587286449</v>
       </c>
       <c r="P50">
-        <v>77.58721955199999</v>
+        <v>77.29155225099998</v>
       </c>
       <c r="Q50">
-        <v>100.487219552</v>
+        <v>100.191552251</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1364855504082925</v>
+        <v>0.1379768740232646</v>
       </c>
       <c r="T50">
-        <v>1.660937703177721</v>
+        <v>1.688251818917154</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.466956954206218</v>
+        <v>6.334978240855071</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08979131575186491</v>
+        <v>0.08958342529141773</v>
       </c>
       <c r="C51">
-        <v>391.374683302039</v>
+        <v>386.8356352749592</v>
       </c>
       <c r="D51">
-        <v>614.965683302039</v>
+        <v>617.8856352749592</v>
       </c>
       <c r="E51">
-        <v>-59.00900000000001</v>
+        <v>-51.55000000000001</v>
       </c>
       <c r="F51">
-        <v>365.491</v>
+        <v>372.95</v>
       </c>
       <c r="G51">
         <v>141.9</v>
@@ -5469,28 +5469,28 @@
         <v>125.725</v>
       </c>
       <c r="M51">
-        <v>19.8461613</v>
+        <v>20.251185</v>
       </c>
       <c r="N51">
-        <v>105.8788387</v>
+        <v>105.473815</v>
       </c>
       <c r="O51">
-        <v>28.587286449</v>
+        <v>28.47793005</v>
       </c>
       <c r="P51">
-        <v>77.29155225099998</v>
+        <v>76.99588495</v>
       </c>
       <c r="Q51">
-        <v>100.191552251</v>
+        <v>99.89588495000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1379768740232646</v>
+        <v>0.1395278505828355</v>
       </c>
       <c r="T51">
-        <v>1.688251818917154</v>
+        <v>1.716658499286164</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.334978240855071</v>
+        <v>6.20827867603797</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08958342529141773</v>
+        <v>0.08974783483097054</v>
       </c>
       <c r="C52">
-        <v>386.8356352749592</v>
+        <v>377.0651154200547</v>
       </c>
       <c r="D52">
-        <v>617.8856352749592</v>
+        <v>615.5741154200547</v>
       </c>
       <c r="E52">
-        <v>-51.55000000000001</v>
+        <v>-44.09100000000001</v>
       </c>
       <c r="F52">
-        <v>372.95</v>
+        <v>380.409</v>
       </c>
       <c r="G52">
         <v>141.9</v>
@@ -5551,45 +5551,45 @@
         <v>125.725</v>
       </c>
       <c r="M52">
-        <v>20.251185</v>
+        <v>21.0366177</v>
       </c>
       <c r="N52">
-        <v>105.473815</v>
+        <v>104.6883823</v>
       </c>
       <c r="O52">
-        <v>28.47793005</v>
+        <v>28.265863221</v>
       </c>
       <c r="P52">
-        <v>76.99588495</v>
+        <v>76.422519079</v>
       </c>
       <c r="Q52">
-        <v>99.89588495000001</v>
+        <v>99.322519079</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1395278505828355</v>
+        <v>0.1411421323081031</v>
       </c>
       <c r="T52">
-        <v>1.716658499286164</v>
+        <v>1.746224635996767</v>
       </c>
       <c r="U52">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>6.20827867603797</v>
+        <v>5.976483567508098</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08974783483097054</v>
+        <v>0.08954724437052333</v>
       </c>
       <c r="C53">
-        <v>377.0651154200547</v>
+        <v>372.4286542342866</v>
       </c>
       <c r="D53">
-        <v>615.5741154200547</v>
+        <v>618.3966542342866</v>
       </c>
       <c r="E53">
-        <v>-44.09100000000001</v>
+        <v>-36.63200000000001</v>
       </c>
       <c r="F53">
-        <v>380.409</v>
+        <v>387.868</v>
       </c>
       <c r="G53">
         <v>141.9</v>
@@ -5633,28 +5633,28 @@
         <v>125.725</v>
       </c>
       <c r="M53">
-        <v>21.0366177</v>
+        <v>21.4491004</v>
       </c>
       <c r="N53">
-        <v>104.6883823</v>
+        <v>104.2758996</v>
       </c>
       <c r="O53">
-        <v>28.265863221</v>
+        <v>28.154492892</v>
       </c>
       <c r="P53">
-        <v>76.422519079</v>
+        <v>76.12140670799999</v>
       </c>
       <c r="Q53">
-        <v>99.322519079</v>
+        <v>99.021406708</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1411421323081031</v>
+        <v>0.1428236757719236</v>
       </c>
       <c r="T53">
-        <v>1.746224635996767</v>
+        <v>1.777022695070312</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.976483567508098</v>
+        <v>5.861551191209866</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08954724437052333</v>
+        <v>0.08934665391007612</v>
       </c>
       <c r="C54">
-        <v>372.4286542342866</v>
+        <v>367.8181961651551</v>
       </c>
       <c r="D54">
-        <v>618.3966542342866</v>
+        <v>621.2451961651551</v>
       </c>
       <c r="E54">
-        <v>-36.63200000000001</v>
+        <v>-29.173</v>
       </c>
       <c r="F54">
-        <v>387.868</v>
+        <v>395.327</v>
       </c>
       <c r="G54">
         <v>141.9</v>
@@ -5715,28 +5715,28 @@
         <v>125.725</v>
       </c>
       <c r="M54">
-        <v>21.4491004</v>
+        <v>21.8615831</v>
       </c>
       <c r="N54">
-        <v>104.2758996</v>
+        <v>103.8634169</v>
       </c>
       <c r="O54">
-        <v>28.154492892</v>
+        <v>28.043122563</v>
       </c>
       <c r="P54">
-        <v>76.12140670799999</v>
+        <v>75.82029433699999</v>
       </c>
       <c r="Q54">
-        <v>99.021406708</v>
+        <v>98.720294337</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1428236757719236</v>
+        <v>0.1445767742767577</v>
       </c>
       <c r="T54">
-        <v>1.777022695070312</v>
+        <v>1.809131309849114</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.861551191209866</v>
+        <v>5.750955885715339</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08934665391007612</v>
+        <v>0.08914606344962893</v>
       </c>
       <c r="C55">
-        <v>367.8181961651551</v>
+        <v>363.2341022127178</v>
       </c>
       <c r="D55">
-        <v>621.2451961651551</v>
+        <v>624.1201022127178</v>
       </c>
       <c r="E55">
-        <v>-29.173</v>
+        <v>-21.714</v>
       </c>
       <c r="F55">
-        <v>395.327</v>
+        <v>402.786</v>
       </c>
       <c r="G55">
         <v>141.9</v>
@@ -5797,28 +5797,28 @@
         <v>125.725</v>
       </c>
       <c r="M55">
-        <v>21.8615831</v>
+        <v>22.2740658</v>
       </c>
       <c r="N55">
-        <v>103.8634169</v>
+        <v>103.4509342</v>
       </c>
       <c r="O55">
-        <v>28.043122563</v>
+        <v>27.931752234</v>
       </c>
       <c r="P55">
-        <v>75.82029433699999</v>
+        <v>75.51918196599999</v>
       </c>
       <c r="Q55">
-        <v>98.720294337</v>
+        <v>98.419181966</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1445767742767577</v>
+        <v>0.1464060944557151</v>
       </c>
       <c r="T55">
-        <v>1.809131309849114</v>
+        <v>1.842635951357429</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.750955885715339</v>
+        <v>5.644456702646536</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08914606344962893</v>
+        <v>0.08894547298918173</v>
       </c>
       <c r="C56">
-        <v>363.2341022127178</v>
+        <v>358.6767400904295</v>
       </c>
       <c r="D56">
-        <v>624.1201022127178</v>
+        <v>627.0217400904295</v>
       </c>
       <c r="E56">
-        <v>-21.714</v>
+        <v>-14.255</v>
       </c>
       <c r="F56">
-        <v>402.786</v>
+        <v>410.245</v>
       </c>
       <c r="G56">
         <v>141.9</v>
@@ -5879,28 +5879,28 @@
         <v>125.725</v>
       </c>
       <c r="M56">
-        <v>22.2740658</v>
+        <v>22.6865485</v>
       </c>
       <c r="N56">
-        <v>103.4509342</v>
+        <v>103.0384515</v>
       </c>
       <c r="O56">
-        <v>27.931752234</v>
+        <v>27.820381905</v>
       </c>
       <c r="P56">
-        <v>75.51918196599999</v>
+        <v>75.21806959499999</v>
       </c>
       <c r="Q56">
-        <v>98.419181966</v>
+        <v>98.11806959499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1464060944557151</v>
+        <v>0.1483167177537372</v>
       </c>
       <c r="T56">
-        <v>1.842635951357429</v>
+        <v>1.877629688043891</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.644456702646536</v>
+        <v>5.541830217143873</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08894547298918173</v>
+        <v>0.08874488252873453</v>
       </c>
       <c r="C57">
-        <v>358.6767400904295</v>
+        <v>354.146484381929</v>
       </c>
       <c r="D57">
-        <v>627.0217400904295</v>
+        <v>629.9504843819291</v>
       </c>
       <c r="E57">
-        <v>-14.255</v>
+        <v>-6.795999999999992</v>
       </c>
       <c r="F57">
-        <v>410.245</v>
+        <v>417.704</v>
       </c>
       <c r="G57">
         <v>141.9</v>
@@ -5961,28 +5961,28 @@
         <v>125.725</v>
       </c>
       <c r="M57">
-        <v>22.6865485</v>
+        <v>23.0990312</v>
       </c>
       <c r="N57">
-        <v>103.0384515</v>
+        <v>102.6259688</v>
       </c>
       <c r="O57">
-        <v>27.820381905</v>
+        <v>27.709011576</v>
       </c>
       <c r="P57">
-        <v>75.21806959499999</v>
+        <v>74.91695722399999</v>
       </c>
       <c r="Q57">
-        <v>98.11806959499999</v>
+        <v>97.81695722399999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1483167177537372</v>
+        <v>0.1503141875653057</v>
       </c>
       <c r="T57">
-        <v>1.877629688043891</v>
+        <v>1.914214049125192</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.541830217143873</v>
+        <v>5.442868963266303</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08874488252873453</v>
+        <v>0.08854429206828734</v>
       </c>
       <c r="C58">
-        <v>354.146484381929</v>
+        <v>349.6437167022403</v>
       </c>
       <c r="D58">
-        <v>629.9504843819291</v>
+        <v>632.9067167022404</v>
       </c>
       <c r="E58">
-        <v>-6.795999999999992</v>
+        <v>0.6630000000000109</v>
       </c>
       <c r="F58">
-        <v>417.704</v>
+        <v>425.163</v>
       </c>
       <c r="G58">
         <v>141.9</v>
@@ -6043,28 +6043,28 @@
         <v>125.725</v>
       </c>
       <c r="M58">
-        <v>23.0990312</v>
+        <v>23.5115139</v>
       </c>
       <c r="N58">
-        <v>102.6259688</v>
+        <v>102.2134861</v>
       </c>
       <c r="O58">
-        <v>27.709011576</v>
+        <v>27.597641247</v>
       </c>
       <c r="P58">
-        <v>74.91695722399999</v>
+        <v>74.615844853</v>
       </c>
       <c r="Q58">
-        <v>97.81695722399999</v>
+        <v>97.515844853</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1503141875653057</v>
+        <v>0.1524045629495054</v>
       </c>
       <c r="T58">
-        <v>1.914214049125192</v>
+        <v>1.952500008396322</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.442868963266303</v>
+        <v>5.347380034086193</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08854429206828734</v>
+        <v>0.08834370160784014</v>
       </c>
       <c r="C59">
-        <v>349.6437167022403</v>
+        <v>345.1688258635371</v>
       </c>
       <c r="D59">
-        <v>632.9067167022404</v>
+        <v>635.8908258635371</v>
       </c>
       <c r="E59">
-        <v>0.6630000000000109</v>
+        <v>8.122000000000014</v>
       </c>
       <c r="F59">
-        <v>425.163</v>
+        <v>432.622</v>
       </c>
       <c r="G59">
         <v>141.9</v>
@@ -6125,28 +6125,28 @@
         <v>125.725</v>
       </c>
       <c r="M59">
-        <v>23.5115139</v>
+        <v>23.9239966</v>
       </c>
       <c r="N59">
-        <v>102.2134861</v>
+        <v>101.8010034</v>
       </c>
       <c r="O59">
-        <v>27.597641247</v>
+        <v>27.486270918</v>
       </c>
       <c r="P59">
-        <v>74.615844853</v>
+        <v>74.31473248199998</v>
       </c>
       <c r="Q59">
-        <v>97.515844853</v>
+        <v>97.21473248199999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1524045629495054</v>
+        <v>0.154594480018667</v>
       </c>
       <c r="T59">
-        <v>1.952500008396322</v>
+        <v>1.992609108585125</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.347380034086193</v>
+        <v>5.255183826601947</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08834370160784011</v>
+        <v>0.08814311114739293</v>
       </c>
       <c r="C60">
-        <v>345.1688258635377</v>
+        <v>340.7222080456144</v>
       </c>
       <c r="D60">
-        <v>635.8908258635377</v>
+        <v>638.9032080456144</v>
       </c>
       <c r="E60">
-        <v>8.121999999999957</v>
+        <v>15.58099999999996</v>
       </c>
       <c r="F60">
-        <v>432.622</v>
+        <v>440.081</v>
       </c>
       <c r="G60">
         <v>141.9</v>
@@ -6207,28 +6207,28 @@
         <v>125.725</v>
       </c>
       <c r="M60">
-        <v>23.9239966</v>
+        <v>24.3364793</v>
       </c>
       <c r="N60">
-        <v>101.8010034</v>
+        <v>101.3885207</v>
       </c>
       <c r="O60">
-        <v>27.486270918</v>
+        <v>27.374900589</v>
       </c>
       <c r="P60">
-        <v>74.314732482</v>
+        <v>74.01362011099999</v>
       </c>
       <c r="Q60">
-        <v>97.214732482</v>
+        <v>96.913620111</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1545944800186669</v>
+        <v>0.1568912223107145</v>
       </c>
       <c r="T60">
-        <v>1.992609108585124</v>
+        <v>2.034674750246551</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.255183826601948</v>
+        <v>5.166112914286662</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08814311114739293</v>
+        <v>0.08794252068694573</v>
       </c>
       <c r="C61">
-        <v>340.7222080456144</v>
+        <v>336.3042669712321</v>
       </c>
       <c r="D61">
-        <v>638.9032080456144</v>
+        <v>641.9442669712321</v>
       </c>
       <c r="E61">
-        <v>15.58099999999996</v>
+        <v>23.03999999999996</v>
       </c>
       <c r="F61">
-        <v>440.081</v>
+        <v>447.54</v>
       </c>
       <c r="G61">
         <v>141.9</v>
@@ -6289,28 +6289,28 @@
         <v>125.725</v>
       </c>
       <c r="M61">
-        <v>24.3364793</v>
+        <v>24.748962</v>
       </c>
       <c r="N61">
-        <v>101.3885207</v>
+        <v>100.976038</v>
       </c>
       <c r="O61">
-        <v>27.374900589</v>
+        <v>27.26353026</v>
       </c>
       <c r="P61">
-        <v>74.01362011099999</v>
+        <v>73.71250773999999</v>
       </c>
       <c r="Q61">
-        <v>96.913620111</v>
+        <v>96.61250774</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1568912223107145</v>
+        <v>0.1593028017173643</v>
       </c>
       <c r="T61">
-        <v>2.034674750246551</v>
+        <v>2.078843673991049</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.166112914286662</v>
+        <v>5.080011032381883</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08794252068694573</v>
+        <v>0.08774193022649854</v>
       </c>
       <c r="C62">
-        <v>336.3042669712321</v>
+        <v>331.9154140864891</v>
       </c>
       <c r="D62">
-        <v>641.9442669712321</v>
+        <v>645.0144140864891</v>
       </c>
       <c r="E62">
-        <v>23.03999999999996</v>
+        <v>30.49899999999997</v>
       </c>
       <c r="F62">
-        <v>447.54</v>
+        <v>454.999</v>
       </c>
       <c r="G62">
         <v>141.9</v>
@@ -6371,28 +6371,28 @@
         <v>125.725</v>
       </c>
       <c r="M62">
-        <v>24.748962</v>
+        <v>25.1614447</v>
       </c>
       <c r="N62">
-        <v>100.976038</v>
+        <v>100.5635553</v>
       </c>
       <c r="O62">
-        <v>27.26353026</v>
+        <v>27.152159931</v>
       </c>
       <c r="P62">
-        <v>73.71250773999999</v>
+        <v>73.41139536899999</v>
       </c>
       <c r="Q62">
-        <v>96.61250774</v>
+        <v>96.311395369</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1593028017173643</v>
+        <v>0.1618380518628167</v>
       </c>
       <c r="T62">
-        <v>2.078843673991049</v>
+        <v>2.125277670748086</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.080011032381883</v>
+        <v>4.996732162998573</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08774193022649854</v>
+        <v>0.08754133976605133</v>
       </c>
       <c r="C63">
-        <v>331.9154140864891</v>
+        <v>327.5560687463983</v>
       </c>
       <c r="D63">
-        <v>645.0144140864891</v>
+        <v>648.1140687463983</v>
       </c>
       <c r="E63">
-        <v>30.49899999999997</v>
+        <v>37.95799999999997</v>
       </c>
       <c r="F63">
-        <v>454.999</v>
+        <v>462.458</v>
       </c>
       <c r="G63">
         <v>141.9</v>
@@ -6453,28 +6453,28 @@
         <v>125.725</v>
       </c>
       <c r="M63">
-        <v>25.1614447</v>
+        <v>25.5739274</v>
       </c>
       <c r="N63">
-        <v>100.5635553</v>
+        <v>100.1510726</v>
       </c>
       <c r="O63">
-        <v>27.152159931</v>
+        <v>27.040789602</v>
       </c>
       <c r="P63">
-        <v>73.41139536899999</v>
+        <v>73.11028299799999</v>
       </c>
       <c r="Q63">
-        <v>96.311395369</v>
+        <v>96.01028299799999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1618380518628167</v>
+        <v>0.1645067362264509</v>
       </c>
       <c r="T63">
-        <v>2.125277670748086</v>
+        <v>2.174155562071282</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.996732162998573</v>
+        <v>4.916139708756662</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08754133976605133</v>
+        <v>0.08734074930560412</v>
       </c>
       <c r="C64">
-        <v>327.5560687463983</v>
+        <v>323.226658405837</v>
       </c>
       <c r="D64">
-        <v>648.1140687463983</v>
+        <v>651.243658405837</v>
       </c>
       <c r="E64">
-        <v>37.95799999999997</v>
+        <v>45.41699999999997</v>
       </c>
       <c r="F64">
-        <v>462.458</v>
+        <v>469.917</v>
       </c>
       <c r="G64">
         <v>141.9</v>
@@ -6535,28 +6535,28 @@
         <v>125.725</v>
       </c>
       <c r="M64">
-        <v>25.5739274</v>
+        <v>25.9864101</v>
       </c>
       <c r="N64">
-        <v>100.1510726</v>
+        <v>99.73858989999999</v>
       </c>
       <c r="O64">
-        <v>27.040789602</v>
+        <v>26.929419273</v>
       </c>
       <c r="P64">
-        <v>73.11028299799999</v>
+        <v>72.80917062699999</v>
       </c>
       <c r="Q64">
-        <v>96.01028299799999</v>
+        <v>95.70917062699999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1645067362264509</v>
+        <v>0.1673196737989301</v>
       </c>
       <c r="T64">
-        <v>2.174155562071282</v>
+        <v>2.22567550157411</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.916139708756662</v>
+        <v>4.838105745125603</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08734074930560412</v>
+        <v>0.08714015884515694</v>
       </c>
       <c r="C65">
-        <v>323.226658405837</v>
+        <v>318.9276188160578</v>
       </c>
       <c r="D65">
-        <v>651.243658405837</v>
+        <v>654.4036188160578</v>
       </c>
       <c r="E65">
-        <v>45.41699999999997</v>
+        <v>52.87599999999998</v>
       </c>
       <c r="F65">
-        <v>469.917</v>
+        <v>477.376</v>
       </c>
       <c r="G65">
         <v>141.9</v>
@@ -6617,28 +6617,28 @@
         <v>125.725</v>
       </c>
       <c r="M65">
-        <v>25.9864101</v>
+        <v>26.3988928</v>
       </c>
       <c r="N65">
-        <v>99.73858989999999</v>
+        <v>99.3261072</v>
       </c>
       <c r="O65">
-        <v>26.929419273</v>
+        <v>26.818048944</v>
       </c>
       <c r="P65">
-        <v>72.80917062699999</v>
+        <v>72.508058256</v>
       </c>
       <c r="Q65">
-        <v>95.70917062699999</v>
+        <v>95.408058256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1673196737989301</v>
+        <v>0.1702888856809915</v>
       </c>
       <c r="T65">
-        <v>2.22567550157411</v>
+        <v>2.280057659938207</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.838105745125603</v>
+        <v>4.762510342858016</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08714015884515694</v>
+        <v>0.08693956838470973</v>
       </c>
       <c r="C66">
-        <v>318.9276188160578</v>
+        <v>314.6593942269495</v>
       </c>
       <c r="D66">
-        <v>654.4036188160578</v>
+        <v>657.5943942269495</v>
       </c>
       <c r="E66">
-        <v>52.87599999999998</v>
+        <v>60.33499999999998</v>
       </c>
       <c r="F66">
-        <v>477.376</v>
+        <v>484.835</v>
       </c>
       <c r="G66">
         <v>141.9</v>
@@ -6699,28 +6699,28 @@
         <v>125.725</v>
       </c>
       <c r="M66">
-        <v>26.3988928</v>
+        <v>26.8113755</v>
       </c>
       <c r="N66">
-        <v>99.3261072</v>
+        <v>98.9136245</v>
       </c>
       <c r="O66">
-        <v>26.818048944</v>
+        <v>26.706678615</v>
       </c>
       <c r="P66">
-        <v>72.508058256</v>
+        <v>72.206945885</v>
       </c>
       <c r="Q66">
-        <v>95.408058256</v>
+        <v>95.106945885</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1702888856809915</v>
+        <v>0.1734277668134564</v>
       </c>
       <c r="T66">
-        <v>2.280057659938207</v>
+        <v>2.337547370208824</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.762510342858016</v>
+        <v>4.689240952967892</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08693956838470973</v>
+        <v>0.08673897792426254</v>
       </c>
       <c r="C67">
-        <v>314.6593942269495</v>
+        <v>310.4224375952404</v>
       </c>
       <c r="D67">
-        <v>657.5943942269495</v>
+        <v>660.8164375952404</v>
       </c>
       <c r="E67">
-        <v>60.33499999999998</v>
+        <v>67.79399999999998</v>
       </c>
       <c r="F67">
-        <v>484.835</v>
+        <v>492.294</v>
       </c>
       <c r="G67">
         <v>141.9</v>
@@ -6781,28 +6781,28 @@
         <v>125.725</v>
       </c>
       <c r="M67">
-        <v>26.8113755</v>
+        <v>27.2238582</v>
       </c>
       <c r="N67">
-        <v>98.9136245</v>
+        <v>98.5011418</v>
       </c>
       <c r="O67">
-        <v>26.706678615</v>
+        <v>26.595308286</v>
       </c>
       <c r="P67">
-        <v>72.206945885</v>
+        <v>71.90583351399999</v>
       </c>
       <c r="Q67">
-        <v>95.106945885</v>
+        <v>94.805833514</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1734277668134564</v>
+        <v>0.1767512880125369</v>
       </c>
       <c r="T67">
-        <v>2.337547370208824</v>
+        <v>2.398418828142418</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.689240952967892</v>
+        <v>4.618191847619894</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08673897792426254</v>
+        <v>0.08653838746381533</v>
       </c>
       <c r="C68">
-        <v>310.4224375952404</v>
+        <v>306.217210798857</v>
       </c>
       <c r="D68">
-        <v>660.8164375952404</v>
+        <v>664.070210798857</v>
       </c>
       <c r="E68">
-        <v>67.79399999999998</v>
+        <v>75.25300000000004</v>
       </c>
       <c r="F68">
-        <v>492.294</v>
+        <v>499.753</v>
       </c>
       <c r="G68">
         <v>141.9</v>
@@ -6863,28 +6863,28 @@
         <v>125.725</v>
       </c>
       <c r="M68">
-        <v>27.2238582</v>
+        <v>27.6363409</v>
       </c>
       <c r="N68">
-        <v>98.5011418</v>
+        <v>98.08865909999999</v>
       </c>
       <c r="O68">
-        <v>26.595308286</v>
+        <v>26.483937957</v>
       </c>
       <c r="P68">
-        <v>71.90583351399999</v>
+        <v>71.60472114299999</v>
       </c>
       <c r="Q68">
-        <v>94.805833514</v>
+        <v>94.504721143</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1767512880125369</v>
+        <v>0.1802762347388344</v>
       </c>
       <c r="T68">
-        <v>2.398418828142418</v>
+        <v>2.462979465344715</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.618191847619894</v>
+        <v>4.549263611088253</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08653838746381533</v>
+        <v>0.08757879700336814</v>
       </c>
       <c r="C69">
-        <v>306.217210798857</v>
+        <v>282.2209949907455</v>
       </c>
       <c r="D69">
-        <v>664.070210798857</v>
+        <v>647.5329949907456</v>
       </c>
       <c r="E69">
-        <v>75.25300000000004</v>
+        <v>82.71200000000005</v>
       </c>
       <c r="F69">
-        <v>499.753</v>
+        <v>507.212</v>
       </c>
       <c r="G69">
         <v>141.9</v>
@@ -6945,45 +6945,45 @@
         <v>125.725</v>
       </c>
       <c r="M69">
-        <v>27.6363409</v>
+        <v>29.31685360000001</v>
       </c>
       <c r="N69">
-        <v>98.08865909999999</v>
+        <v>96.40814639999999</v>
       </c>
       <c r="O69">
-        <v>26.483937957</v>
+        <v>26.030199528</v>
       </c>
       <c r="P69">
-        <v>71.60472114299999</v>
+        <v>70.377946872</v>
       </c>
       <c r="Q69">
-        <v>94.504721143</v>
+        <v>93.277946872</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1802762347388344</v>
+        <v>0.1840214906355254</v>
       </c>
       <c r="T69">
-        <v>2.462979465344715</v>
+        <v>2.531575142372155</v>
       </c>
       <c r="U69">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V69">
         <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.549263611088253</v>
+        <v>4.28848885748094</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08757879700336814</v>
+        <v>0.08739645654292093</v>
       </c>
       <c r="C70">
-        <v>282.2209949907455</v>
+        <v>277.6004931291518</v>
       </c>
       <c r="D70">
-        <v>647.5329949907456</v>
+        <v>650.3714931291519</v>
       </c>
       <c r="E70">
-        <v>82.71200000000005</v>
+        <v>90.17100000000005</v>
       </c>
       <c r="F70">
-        <v>507.212</v>
+        <v>514.671</v>
       </c>
       <c r="G70">
         <v>141.9</v>
@@ -7027,28 +7027,28 @@
         <v>125.725</v>
       </c>
       <c r="M70">
-        <v>29.31685360000001</v>
+        <v>29.7479838</v>
       </c>
       <c r="N70">
-        <v>96.40814639999999</v>
+        <v>95.97701619999999</v>
       </c>
       <c r="O70">
-        <v>26.030199528</v>
+        <v>25.913794374</v>
       </c>
       <c r="P70">
-        <v>70.377946872</v>
+        <v>70.06322182599999</v>
       </c>
       <c r="Q70">
-        <v>93.277946872</v>
+        <v>92.96322182599999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1840214906355254</v>
+        <v>0.1880083759449062</v>
       </c>
       <c r="T70">
-        <v>2.531575142372155</v>
+        <v>2.604596346949752</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.28848885748094</v>
+        <v>4.22633684505368</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08739645654292093</v>
+        <v>0.08721411608247374</v>
       </c>
       <c r="C71">
-        <v>277.6004931291518</v>
+        <v>273.0049862744053</v>
       </c>
       <c r="D71">
-        <v>650.3714931291519</v>
+        <v>653.2349862744053</v>
       </c>
       <c r="E71">
-        <v>90.17100000000005</v>
+        <v>97.63</v>
       </c>
       <c r="F71">
-        <v>514.671</v>
+        <v>522.13</v>
       </c>
       <c r="G71">
         <v>141.9</v>
@@ -7109,28 +7109,28 @@
         <v>125.725</v>
       </c>
       <c r="M71">
-        <v>29.7479838</v>
+        <v>30.179114</v>
       </c>
       <c r="N71">
-        <v>95.97701619999999</v>
+        <v>95.545886</v>
       </c>
       <c r="O71">
-        <v>25.913794374</v>
+        <v>25.79738922</v>
       </c>
       <c r="P71">
-        <v>70.06322182599999</v>
+        <v>69.74849678</v>
       </c>
       <c r="Q71">
-        <v>92.96322182599999</v>
+        <v>92.64849678</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1880083759449062</v>
+        <v>0.1922610536082458</v>
       </c>
       <c r="T71">
-        <v>2.604596346949752</v>
+        <v>2.682485631832524</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.22633684505368</v>
+        <v>4.165960604410056</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08721411608247374</v>
+        <v>0.08703177562202653</v>
       </c>
       <c r="C72">
-        <v>273.0049862744053</v>
+        <v>268.4348060349073</v>
       </c>
       <c r="D72">
-        <v>653.2349862744053</v>
+        <v>656.1238060349074</v>
       </c>
       <c r="E72">
-        <v>97.63</v>
+        <v>105.0890000000001</v>
       </c>
       <c r="F72">
-        <v>522.13</v>
+        <v>529.5890000000001</v>
       </c>
       <c r="G72">
         <v>141.9</v>
@@ -7191,28 +7191,28 @@
         <v>125.725</v>
       </c>
       <c r="M72">
-        <v>30.179114</v>
+        <v>30.6102442</v>
       </c>
       <c r="N72">
-        <v>95.545886</v>
+        <v>95.11475579999998</v>
       </c>
       <c r="O72">
-        <v>25.79738922</v>
+        <v>25.680984066</v>
       </c>
       <c r="P72">
-        <v>69.74849678</v>
+        <v>69.43377173399999</v>
       </c>
       <c r="Q72">
-        <v>92.64849678</v>
+        <v>92.333771734</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1922610536082458</v>
+        <v>0.1968070193862984</v>
       </c>
       <c r="T72">
-        <v>2.682485631832524</v>
+        <v>2.765746591534796</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.165960604410056</v>
+        <v>4.107285102939492</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08703177562202653</v>
+        <v>0.08684943516157934</v>
       </c>
       <c r="C73">
-        <v>268.4348060349074</v>
+        <v>263.8902899110399</v>
       </c>
       <c r="D73">
-        <v>656.1238060349074</v>
+        <v>659.0382899110399</v>
       </c>
       <c r="E73">
-        <v>105.0889999999999</v>
+        <v>112.548</v>
       </c>
       <c r="F73">
-        <v>529.5889999999999</v>
+        <v>537.048</v>
       </c>
       <c r="G73">
         <v>141.9</v>
@@ -7273,28 +7273,28 @@
         <v>125.725</v>
       </c>
       <c r="M73">
-        <v>30.6102442</v>
+        <v>31.0413744</v>
       </c>
       <c r="N73">
-        <v>95.1147558</v>
+        <v>94.6836256</v>
       </c>
       <c r="O73">
-        <v>25.680984066</v>
+        <v>25.564578912</v>
       </c>
       <c r="P73">
-        <v>69.433771734</v>
+        <v>69.119046688</v>
       </c>
       <c r="Q73">
-        <v>92.33377173400001</v>
+        <v>92.019046688</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1968070193862984</v>
+        <v>0.2016776970056405</v>
       </c>
       <c r="T73">
-        <v>2.765746591534795</v>
+        <v>2.854954762644373</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.107285102939493</v>
+        <v>4.050239476509777</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08684943516157934</v>
+        <v>0.08853224470113213</v>
       </c>
       <c r="C74">
-        <v>263.8902899110399</v>
+        <v>230.4781500994195</v>
       </c>
       <c r="D74">
-        <v>659.0382899110399</v>
+        <v>633.0851500994195</v>
       </c>
       <c r="E74">
-        <v>112.548</v>
+        <v>120.0069999999999</v>
       </c>
       <c r="F74">
-        <v>537.048</v>
+        <v>544.5069999999999</v>
       </c>
       <c r="G74">
         <v>141.9</v>
@@ -7355,45 +7355,45 @@
         <v>125.725</v>
       </c>
       <c r="M74">
-        <v>31.0413744</v>
+        <v>33.3782791</v>
       </c>
       <c r="N74">
-        <v>94.6836256</v>
+        <v>92.34672089999999</v>
       </c>
       <c r="O74">
-        <v>25.564578912</v>
+        <v>24.933614643</v>
       </c>
       <c r="P74">
-        <v>69.119046688</v>
+        <v>67.413106257</v>
       </c>
       <c r="Q74">
-        <v>92.019046688</v>
+        <v>90.313106257</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2016776970056405</v>
+        <v>0.2069091655597486</v>
       </c>
       <c r="T74">
-        <v>2.854954762644373</v>
+        <v>2.950770946428733</v>
       </c>
       <c r="U74">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V74">
         <v>0.27</v>
       </c>
       <c r="W74">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.050239476509777</v>
+        <v>3.766671122358732</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08853224470113213</v>
+        <v>0.08837545424068494</v>
       </c>
       <c r="C75">
-        <v>230.4781500994195</v>
+        <v>225.3505805904538</v>
       </c>
       <c r="D75">
-        <v>633.0851500994195</v>
+        <v>635.4165805904538</v>
       </c>
       <c r="E75">
-        <v>120.0069999999999</v>
+        <v>127.466</v>
       </c>
       <c r="F75">
-        <v>544.5069999999999</v>
+        <v>551.966</v>
       </c>
       <c r="G75">
         <v>141.9</v>
@@ -7437,28 +7437,28 @@
         <v>125.725</v>
       </c>
       <c r="M75">
-        <v>33.3782791</v>
+        <v>33.8355158</v>
       </c>
       <c r="N75">
-        <v>92.34672089999999</v>
+        <v>91.8894842</v>
       </c>
       <c r="O75">
-        <v>24.933614643</v>
+        <v>24.810160734</v>
       </c>
       <c r="P75">
-        <v>67.413106257</v>
+        <v>67.07932346600001</v>
       </c>
       <c r="Q75">
-        <v>90.313106257</v>
+        <v>89.97932346600001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2069091655597486</v>
+        <v>0.2125430547718651</v>
       </c>
       <c r="T75">
-        <v>2.950770946428733</v>
+        <v>3.053957605888815</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.766671122358732</v>
+        <v>3.715770161245776</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08837545424068494</v>
+        <v>0.08821866378023774</v>
       </c>
       <c r="C76">
-        <v>225.3505805904538</v>
+        <v>220.2402462335469</v>
       </c>
       <c r="D76">
-        <v>635.4165805904538</v>
+        <v>637.7652462335469</v>
       </c>
       <c r="E76">
-        <v>127.466</v>
+        <v>134.925</v>
       </c>
       <c r="F76">
-        <v>551.966</v>
+        <v>559.425</v>
       </c>
       <c r="G76">
         <v>141.9</v>
@@ -7519,28 +7519,28 @@
         <v>125.725</v>
       </c>
       <c r="M76">
-        <v>33.8355158</v>
+        <v>34.2927525</v>
       </c>
       <c r="N76">
-        <v>91.8894842</v>
+        <v>91.43224749999999</v>
       </c>
       <c r="O76">
-        <v>24.810160734</v>
+        <v>24.686706825</v>
       </c>
       <c r="P76">
-        <v>67.07932346600001</v>
+        <v>66.74554067499999</v>
       </c>
       <c r="Q76">
-        <v>89.97932346600001</v>
+        <v>89.64554067499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2125430547718651</v>
+        <v>0.2186276551209509</v>
       </c>
       <c r="T76">
-        <v>3.053957605888815</v>
+        <v>3.165399198105702</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.715770161245776</v>
+        <v>3.666226559095832</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08821866378023774</v>
+        <v>0.08806187331979053</v>
       </c>
       <c r="C77">
-        <v>220.2402462335469</v>
+        <v>215.1473388546083</v>
       </c>
       <c r="D77">
-        <v>637.7652462335469</v>
+        <v>640.1313388546083</v>
       </c>
       <c r="E77">
-        <v>134.925</v>
+        <v>142.384</v>
       </c>
       <c r="F77">
-        <v>559.425</v>
+        <v>566.884</v>
       </c>
       <c r="G77">
         <v>141.9</v>
@@ -7601,28 +7601,28 @@
         <v>125.725</v>
       </c>
       <c r="M77">
-        <v>34.2927525</v>
+        <v>34.7499892</v>
       </c>
       <c r="N77">
-        <v>91.43224749999999</v>
+        <v>90.97501079999999</v>
       </c>
       <c r="O77">
-        <v>24.686706825</v>
+        <v>24.563252916</v>
       </c>
       <c r="P77">
-        <v>66.74554067499999</v>
+        <v>66.411757884</v>
       </c>
       <c r="Q77">
-        <v>89.64554067499999</v>
+        <v>89.311757884</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2186276551209509</v>
+        <v>0.2252193054991272</v>
       </c>
       <c r="T77">
-        <v>3.165399198105702</v>
+        <v>3.286127589673997</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.666226559095832</v>
+        <v>3.617986735949834</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08806187331979053</v>
+        <v>0.08790508285934333</v>
       </c>
       <c r="C78">
-        <v>215.1473388546083</v>
+        <v>210.072053136824</v>
       </c>
       <c r="D78">
-        <v>640.1313388546083</v>
+        <v>642.515053136824</v>
       </c>
       <c r="E78">
-        <v>142.384</v>
+        <v>149.843</v>
       </c>
       <c r="F78">
-        <v>566.884</v>
+        <v>574.343</v>
       </c>
       <c r="G78">
         <v>141.9</v>
@@ -7683,28 +7683,28 @@
         <v>125.725</v>
       </c>
       <c r="M78">
-        <v>34.7499892</v>
+        <v>35.2072259</v>
       </c>
       <c r="N78">
-        <v>90.97501079999999</v>
+        <v>90.5177741</v>
       </c>
       <c r="O78">
-        <v>24.563252916</v>
+        <v>24.439799007</v>
       </c>
       <c r="P78">
-        <v>66.411757884</v>
+        <v>66.07797509299999</v>
       </c>
       <c r="Q78">
-        <v>89.311757884</v>
+        <v>88.977975093</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2252193054991272</v>
+        <v>0.2323841428667101</v>
       </c>
       <c r="T78">
-        <v>3.286127589673997</v>
+        <v>3.41735410224823</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.617986735949834</v>
+        <v>3.570999895223213</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08790508285934333</v>
+        <v>0.08774829239889612</v>
       </c>
       <c r="C79">
-        <v>210.072053136824</v>
+        <v>205.0145866740567</v>
       </c>
       <c r="D79">
-        <v>642.515053136824</v>
+        <v>644.9165866740567</v>
       </c>
       <c r="E79">
-        <v>149.843</v>
+        <v>157.302</v>
       </c>
       <c r="F79">
-        <v>574.343</v>
+        <v>581.802</v>
       </c>
       <c r="G79">
         <v>141.9</v>
@@ -7765,28 +7765,28 @@
         <v>125.725</v>
       </c>
       <c r="M79">
-        <v>35.2072259</v>
+        <v>35.6644626</v>
       </c>
       <c r="N79">
-        <v>90.5177741</v>
+        <v>90.06053739999999</v>
       </c>
       <c r="O79">
-        <v>24.439799007</v>
+        <v>24.316345098</v>
       </c>
       <c r="P79">
-        <v>66.07797509299999</v>
+        <v>65.74419230199999</v>
       </c>
       <c r="Q79">
-        <v>88.977975093</v>
+        <v>88.64419230199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2323841428667101</v>
+        <v>0.2402003290858915</v>
       </c>
       <c r="T79">
-        <v>3.41735410224823</v>
+        <v>3.560510297783758</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.570999895223213</v>
+        <v>3.525217845284454</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08774829239889612</v>
+        <v>0.08920626193844894</v>
       </c>
       <c r="C80">
-        <v>205.0145866740567</v>
+        <v>175.8935338518976</v>
       </c>
       <c r="D80">
-        <v>644.9165866740567</v>
+        <v>623.2545338518976</v>
       </c>
       <c r="E80">
-        <v>157.302</v>
+        <v>164.761</v>
       </c>
       <c r="F80">
-        <v>581.802</v>
+        <v>589.261</v>
       </c>
       <c r="G80">
         <v>141.9</v>
@@ -7847,45 +7847,45 @@
         <v>125.725</v>
       </c>
       <c r="M80">
-        <v>35.6644626</v>
+        <v>37.7716301</v>
       </c>
       <c r="N80">
-        <v>90.06053739999999</v>
+        <v>87.95336989999998</v>
       </c>
       <c r="O80">
-        <v>24.316345098</v>
+        <v>23.747409873</v>
       </c>
       <c r="P80">
-        <v>65.74419230199999</v>
+        <v>64.20596002699999</v>
       </c>
       <c r="Q80">
-        <v>88.64419230199999</v>
+        <v>87.10596002699999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2402003290858915</v>
+        <v>0.248760913992614</v>
       </c>
       <c r="T80">
-        <v>3.560510297783758</v>
+        <v>3.717300416703622</v>
       </c>
       <c r="U80">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>3.525217845284454</v>
+        <v>3.328556370671436</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08920626193844894</v>
+        <v>0.08906991147800172</v>
       </c>
       <c r="C81">
-        <v>175.8935338518976</v>
+        <v>170.3985092741659</v>
       </c>
       <c r="D81">
-        <v>623.2545338518976</v>
+        <v>625.218509274166</v>
       </c>
       <c r="E81">
-        <v>164.761</v>
+        <v>172.22</v>
       </c>
       <c r="F81">
-        <v>589.261</v>
+        <v>596.72</v>
       </c>
       <c r="G81">
         <v>141.9</v>
@@ -7929,28 +7929,28 @@
         <v>125.725</v>
       </c>
       <c r="M81">
-        <v>37.7716301</v>
+        <v>38.249752</v>
       </c>
       <c r="N81">
-        <v>87.95336989999998</v>
+        <v>87.47524799999999</v>
       </c>
       <c r="O81">
-        <v>23.747409873</v>
+        <v>23.61831696</v>
       </c>
       <c r="P81">
-        <v>64.20596002699999</v>
+        <v>63.85693103999999</v>
       </c>
       <c r="Q81">
-        <v>87.10596002699999</v>
+        <v>86.75693104</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.248760913992614</v>
+        <v>0.2581775573900087</v>
       </c>
       <c r="T81">
-        <v>3.717300416703622</v>
+        <v>3.889769547515471</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.328556370671436</v>
+        <v>3.286949416038043</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08906991147800172</v>
+        <v>0.08893356101755452</v>
       </c>
       <c r="C82">
-        <v>170.3985092741659</v>
+        <v>164.915901429336</v>
       </c>
       <c r="D82">
-        <v>625.218509274166</v>
+        <v>627.194901429336</v>
       </c>
       <c r="E82">
-        <v>172.22</v>
+        <v>179.679</v>
       </c>
       <c r="F82">
-        <v>596.72</v>
+        <v>604.179</v>
       </c>
       <c r="G82">
         <v>141.9</v>
@@ -8011,28 +8011,28 @@
         <v>125.725</v>
       </c>
       <c r="M82">
-        <v>38.249752</v>
+        <v>38.7278739</v>
       </c>
       <c r="N82">
-        <v>87.47524799999999</v>
+        <v>86.9971261</v>
       </c>
       <c r="O82">
-        <v>23.61831696</v>
+        <v>23.489224047</v>
       </c>
       <c r="P82">
-        <v>63.85693103999999</v>
+        <v>63.507902053</v>
       </c>
       <c r="Q82">
-        <v>86.75693104</v>
+        <v>86.407902053</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2581775573900087</v>
+        <v>0.2685854264081817</v>
       </c>
       <c r="T82">
-        <v>3.889769547515471</v>
+        <v>4.080393323675937</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.286949416038043</v>
+        <v>3.246369793617821</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08893356101755452</v>
+        <v>0.08879721055710732</v>
       </c>
       <c r="C83">
-        <v>164.915901429336</v>
+        <v>159.4458284432511</v>
       </c>
       <c r="D83">
-        <v>627.194901429336</v>
+        <v>629.1838284432512</v>
       </c>
       <c r="E83">
-        <v>179.679</v>
+        <v>187.138</v>
       </c>
       <c r="F83">
-        <v>604.179</v>
+        <v>611.638</v>
       </c>
       <c r="G83">
         <v>141.9</v>
@@ -8093,28 +8093,28 @@
         <v>125.725</v>
       </c>
       <c r="M83">
-        <v>38.7278739</v>
+        <v>39.2059958</v>
       </c>
       <c r="N83">
-        <v>86.9971261</v>
+        <v>86.51900419999998</v>
       </c>
       <c r="O83">
-        <v>23.489224047</v>
+        <v>23.360131134</v>
       </c>
       <c r="P83">
-        <v>63.507902053</v>
+        <v>63.15887306599998</v>
       </c>
       <c r="Q83">
-        <v>86.407902053</v>
+        <v>86.05887306599999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2685854264081817</v>
+        <v>0.280149725317263</v>
       </c>
       <c r="T83">
-        <v>4.080393323675937</v>
+        <v>4.292197519409788</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.246369793617821</v>
+        <v>3.206779918085896</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08879721055710732</v>
+        <v>0.08866086009666013</v>
       </c>
       <c r="C84">
-        <v>159.4458284432511</v>
+        <v>153.9884099448983</v>
       </c>
       <c r="D84">
-        <v>629.1838284432512</v>
+        <v>631.1854099448983</v>
       </c>
       <c r="E84">
-        <v>187.138</v>
+        <v>194.597</v>
       </c>
       <c r="F84">
-        <v>611.638</v>
+        <v>619.097</v>
       </c>
       <c r="G84">
         <v>141.9</v>
@@ -8175,28 +8175,28 @@
         <v>125.725</v>
       </c>
       <c r="M84">
-        <v>39.2059958</v>
+        <v>39.6841177</v>
       </c>
       <c r="N84">
-        <v>86.51900419999998</v>
+        <v>86.04088229999999</v>
       </c>
       <c r="O84">
-        <v>23.360131134</v>
+        <v>23.231038221</v>
       </c>
       <c r="P84">
-        <v>63.15887306599998</v>
+        <v>62.80984407899999</v>
       </c>
       <c r="Q84">
-        <v>86.05887306599999</v>
+        <v>85.70984407899999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.280149725317263</v>
+        <v>0.2930745299803538</v>
       </c>
       <c r="T84">
-        <v>4.292197519409788</v>
+        <v>4.52891985581821</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.206779918085896</v>
+        <v>3.168144015458355</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08866086009666013</v>
+        <v>0.08852450963621294</v>
       </c>
       <c r="C85">
-        <v>153.9884099448983</v>
+        <v>148.5437670903946</v>
       </c>
       <c r="D85">
-        <v>631.1854099448983</v>
+        <v>633.1997670903946</v>
       </c>
       <c r="E85">
-        <v>194.597</v>
+        <v>202.056</v>
       </c>
       <c r="F85">
-        <v>619.097</v>
+        <v>626.556</v>
       </c>
       <c r="G85">
         <v>141.9</v>
@@ -8257,28 +8257,28 @@
         <v>125.725</v>
       </c>
       <c r="M85">
-        <v>39.6841177</v>
+        <v>40.16223960000001</v>
       </c>
       <c r="N85">
-        <v>86.04088229999999</v>
+        <v>85.56276039999999</v>
       </c>
       <c r="O85">
-        <v>23.231038221</v>
+        <v>23.101945308</v>
       </c>
       <c r="P85">
-        <v>62.80984407899999</v>
+        <v>62.46081509199999</v>
       </c>
       <c r="Q85">
-        <v>85.70984407899999</v>
+        <v>85.360815092</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2930745299803538</v>
+        <v>0.307614935226331</v>
       </c>
       <c r="T85">
-        <v>4.52891985581821</v>
+        <v>4.795232484277685</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.168144015458355</v>
+        <v>3.130428015274327</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08852450963621294</v>
+        <v>0.08838815917576573</v>
       </c>
       <c r="C86">
-        <v>148.5437670903947</v>
+        <v>143.1120225874337</v>
       </c>
       <c r="D86">
-        <v>633.1997670903946</v>
+        <v>635.2270225874337</v>
       </c>
       <c r="E86">
-        <v>202.0559999999999</v>
+        <v>209.515</v>
       </c>
       <c r="F86">
-        <v>626.5559999999999</v>
+        <v>634.015</v>
       </c>
       <c r="G86">
         <v>141.9</v>
@@ -8339,28 +8339,28 @@
         <v>125.725</v>
       </c>
       <c r="M86">
-        <v>40.1622396</v>
+        <v>40.6403615</v>
       </c>
       <c r="N86">
-        <v>85.5627604</v>
+        <v>85.08463849999998</v>
       </c>
       <c r="O86">
-        <v>23.101945308</v>
+        <v>22.972852395</v>
       </c>
       <c r="P86">
-        <v>62.460815092</v>
+        <v>62.11178610499999</v>
       </c>
       <c r="Q86">
-        <v>85.36081509200001</v>
+        <v>85.011786105</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3076149352263308</v>
+        <v>0.3240940611717715</v>
       </c>
       <c r="T86">
-        <v>4.795232484277681</v>
+        <v>5.097053463198418</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.130428015274327</v>
+        <v>3.093599450388747</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08838815917576573</v>
+        <v>0.08825180871531854</v>
       </c>
       <c r="C87">
-        <v>143.1120225874337</v>
+        <v>137.6933007202013</v>
       </c>
       <c r="D87">
-        <v>635.2270225874337</v>
+        <v>637.2673007202012</v>
       </c>
       <c r="E87">
-        <v>209.515</v>
+        <v>216.9739999999999</v>
       </c>
       <c r="F87">
-        <v>634.015</v>
+        <v>641.4739999999999</v>
       </c>
       <c r="G87">
         <v>141.9</v>
@@ -8421,28 +8421,28 @@
         <v>125.725</v>
       </c>
       <c r="M87">
-        <v>40.6403615</v>
+        <v>41.1184834</v>
       </c>
       <c r="N87">
-        <v>85.08463849999998</v>
+        <v>84.60651659999999</v>
       </c>
       <c r="O87">
-        <v>22.972852395</v>
+        <v>22.843759482</v>
       </c>
       <c r="P87">
-        <v>62.11178610499999</v>
+        <v>61.762757118</v>
       </c>
       <c r="Q87">
-        <v>85.011786105</v>
+        <v>84.662757118</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3240940611717715</v>
+        <v>0.3429273479665609</v>
       </c>
       <c r="T87">
-        <v>5.097053463198418</v>
+        <v>5.441991724822119</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.093599450388747</v>
+        <v>3.05762736375632</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08825180871531854</v>
+        <v>0.08811545825487133</v>
       </c>
       <c r="C88">
-        <v>137.6933007202013</v>
+        <v>132.2877273747773</v>
       </c>
       <c r="D88">
-        <v>637.2673007202012</v>
+        <v>639.3207273747773</v>
       </c>
       <c r="E88">
-        <v>216.9739999999999</v>
+        <v>224.433</v>
       </c>
       <c r="F88">
-        <v>641.4739999999999</v>
+        <v>648.933</v>
       </c>
       <c r="G88">
         <v>141.9</v>
@@ -8503,28 +8503,28 @@
         <v>125.725</v>
       </c>
       <c r="M88">
-        <v>41.1184834</v>
+        <v>41.5966053</v>
       </c>
       <c r="N88">
-        <v>84.60651659999999</v>
+        <v>84.1283947</v>
       </c>
       <c r="O88">
-        <v>22.843759482</v>
+        <v>22.714666569</v>
       </c>
       <c r="P88">
-        <v>61.762757118</v>
+        <v>61.413728131</v>
       </c>
       <c r="Q88">
-        <v>84.662757118</v>
+        <v>84.313728131</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3429273479665609</v>
+        <v>0.3646580634990102</v>
       </c>
       <c r="T88">
-        <v>5.441991724822119</v>
+        <v>5.839997411311002</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.05762736375632</v>
+        <v>3.022482221644178</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08811545825487133</v>
+        <v>0.09298982779442413</v>
       </c>
       <c r="C89">
-        <v>132.2877273747773</v>
+        <v>58.79149805713666</v>
       </c>
       <c r="D89">
-        <v>639.3207273747773</v>
+        <v>573.2834980571366</v>
       </c>
       <c r="E89">
-        <v>224.433</v>
+        <v>231.8919999999999</v>
       </c>
       <c r="F89">
-        <v>648.933</v>
+        <v>656.3919999999999</v>
       </c>
       <c r="G89">
         <v>141.9</v>
@@ -8585,45 +8585,45 @@
         <v>125.725</v>
       </c>
       <c r="M89">
-        <v>41.5966053</v>
+        <v>47.1945848</v>
       </c>
       <c r="N89">
-        <v>84.1283947</v>
+        <v>78.53041519999999</v>
       </c>
       <c r="O89">
-        <v>22.714666569</v>
+        <v>21.203212104</v>
       </c>
       <c r="P89">
-        <v>61.413728131</v>
+        <v>57.32720309599999</v>
       </c>
       <c r="Q89">
-        <v>84.313728131</v>
+        <v>80.227203096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3646580634990102</v>
+        <v>0.3900105649535345</v>
       </c>
       <c r="T89">
-        <v>5.839997411311002</v>
+        <v>6.304337378881367</v>
       </c>
       <c r="U89">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V89">
         <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>3.022482221644178</v>
+        <v>2.663970888456677</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09298982779442413</v>
+        <v>0.09291041733397694</v>
       </c>
       <c r="C90">
-        <v>58.79149805713666</v>
+        <v>52.29883860608061</v>
       </c>
       <c r="D90">
-        <v>573.2834980571366</v>
+        <v>574.2498386060806</v>
       </c>
       <c r="E90">
-        <v>231.8919999999999</v>
+        <v>239.351</v>
       </c>
       <c r="F90">
-        <v>656.3919999999999</v>
+        <v>663.851</v>
       </c>
       <c r="G90">
         <v>141.9</v>
@@ -8667,28 +8667,28 @@
         <v>125.725</v>
       </c>
       <c r="M90">
-        <v>47.1945848</v>
+        <v>47.7308869</v>
       </c>
       <c r="N90">
-        <v>78.53041519999999</v>
+        <v>77.99411309999999</v>
       </c>
       <c r="O90">
-        <v>21.203212104</v>
+        <v>21.058410537</v>
       </c>
       <c r="P90">
-        <v>57.32720309599999</v>
+        <v>56.93570256299999</v>
       </c>
       <c r="Q90">
-        <v>80.227203096</v>
+        <v>79.835702563</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3900105649535345</v>
+        <v>0.419972612127063</v>
       </c>
       <c r="T90">
-        <v>6.304337378881367</v>
+        <v>6.85310279510089</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.663970888456677</v>
+        <v>2.634038631283007</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09291041733397694</v>
+        <v>0.09283100687352974</v>
       </c>
       <c r="C91">
-        <v>52.29883860608061</v>
+        <v>45.80944242974658</v>
       </c>
       <c r="D91">
-        <v>574.2498386060806</v>
+        <v>575.2194424297466</v>
       </c>
       <c r="E91">
-        <v>239.351</v>
+        <v>246.8099999999999</v>
       </c>
       <c r="F91">
-        <v>663.851</v>
+        <v>671.3099999999999</v>
       </c>
       <c r="G91">
         <v>141.9</v>
@@ -8749,28 +8749,28 @@
         <v>125.725</v>
       </c>
       <c r="M91">
-        <v>47.7308869</v>
+        <v>48.267189</v>
       </c>
       <c r="N91">
-        <v>77.99411309999999</v>
+        <v>77.45781099999999</v>
       </c>
       <c r="O91">
-        <v>21.058410537</v>
+        <v>20.91360897</v>
       </c>
       <c r="P91">
-        <v>56.93570256299999</v>
+        <v>56.54420202999999</v>
       </c>
       <c r="Q91">
-        <v>79.835702563</v>
+        <v>79.44420203</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.419972612127063</v>
+        <v>0.4559270687352974</v>
       </c>
       <c r="T91">
-        <v>6.85310279510089</v>
+        <v>7.511621294564317</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.634038631283007</v>
+        <v>2.604771535379862</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09283100687352974</v>
+        <v>0.09275159641308253</v>
       </c>
       <c r="C92">
-        <v>45.80944242974658</v>
+        <v>39.32332608591992</v>
       </c>
       <c r="D92">
-        <v>575.2194424297466</v>
+        <v>576.1923260859199</v>
       </c>
       <c r="E92">
-        <v>246.8099999999999</v>
+        <v>254.269</v>
       </c>
       <c r="F92">
-        <v>671.3099999999999</v>
+        <v>678.769</v>
       </c>
       <c r="G92">
         <v>141.9</v>
@@ -8831,28 +8831,28 @@
         <v>125.725</v>
       </c>
       <c r="M92">
-        <v>48.267189</v>
+        <v>48.8034911</v>
       </c>
       <c r="N92">
-        <v>77.45781099999999</v>
+        <v>76.92150889999999</v>
       </c>
       <c r="O92">
-        <v>20.91360897</v>
+        <v>20.768807403</v>
       </c>
       <c r="P92">
-        <v>56.54420202999999</v>
+        <v>56.152701497</v>
       </c>
       <c r="Q92">
-        <v>79.44420203</v>
+        <v>79.052701497</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4559270687352974</v>
+        <v>0.4998714045898061</v>
       </c>
       <c r="T92">
-        <v>7.511621294564317</v>
+        <v>8.316477238352951</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.604771535379862</v>
+        <v>2.57614767235371</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09275159641308253</v>
+        <v>0.09267218595263534</v>
       </c>
       <c r="C93">
-        <v>39.32332608591992</v>
+        <v>32.84050624459348</v>
       </c>
       <c r="D93">
-        <v>576.1923260859199</v>
+        <v>577.1685062445936</v>
       </c>
       <c r="E93">
-        <v>254.269</v>
+        <v>261.7280000000001</v>
       </c>
       <c r="F93">
-        <v>678.769</v>
+        <v>686.2280000000001</v>
       </c>
       <c r="G93">
         <v>141.9</v>
@@ -8913,28 +8913,28 @@
         <v>125.725</v>
       </c>
       <c r="M93">
-        <v>48.8034911</v>
+        <v>49.33979320000001</v>
       </c>
       <c r="N93">
-        <v>76.92150889999999</v>
+        <v>76.38520679999999</v>
       </c>
       <c r="O93">
-        <v>20.768807403</v>
+        <v>20.624005836</v>
       </c>
       <c r="P93">
-        <v>56.152701497</v>
+        <v>55.761200964</v>
       </c>
       <c r="Q93">
-        <v>79.052701497</v>
+        <v>78.661200964</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4998714045898061</v>
+        <v>0.5548018244079419</v>
       </c>
       <c r="T93">
-        <v>8.316477238352951</v>
+        <v>9.322547168088743</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.57614767235371</v>
+        <v>2.54814606721943</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09267218595263534</v>
+        <v>0.09259277549218814</v>
       </c>
       <c r="C94">
-        <v>32.84050624459348</v>
+        <v>26.36099968892142</v>
       </c>
       <c r="D94">
-        <v>577.1685062445936</v>
+        <v>578.1479996889215</v>
       </c>
       <c r="E94">
-        <v>261.7280000000001</v>
+        <v>269.187</v>
       </c>
       <c r="F94">
-        <v>686.2280000000001</v>
+        <v>693.687</v>
       </c>
       <c r="G94">
         <v>141.9</v>
@@ -8995,28 +8995,28 @@
         <v>125.725</v>
       </c>
       <c r="M94">
-        <v>49.33979320000001</v>
+        <v>49.8760953</v>
       </c>
       <c r="N94">
-        <v>76.38520679999999</v>
+        <v>75.84890469999999</v>
       </c>
       <c r="O94">
-        <v>20.624005836</v>
+        <v>20.479204269</v>
       </c>
       <c r="P94">
-        <v>55.761200964</v>
+        <v>55.36970043099999</v>
       </c>
       <c r="Q94">
-        <v>78.661200964</v>
+        <v>78.26970043099999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5548018244079419</v>
+        <v>0.6254266498884022</v>
       </c>
       <c r="T94">
-        <v>9.322547168088743</v>
+        <v>10.61606564917762</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.54814606721943</v>
+        <v>2.520746647141802</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09259277549218814</v>
+        <v>0.09518954503174093</v>
       </c>
       <c r="C95">
-        <v>26.36099968892142</v>
+        <v>-11.49546831732823</v>
       </c>
       <c r="D95">
-        <v>578.1479996889215</v>
+        <v>547.7505316826719</v>
       </c>
       <c r="E95">
-        <v>269.187</v>
+        <v>276.6460000000001</v>
       </c>
       <c r="F95">
-        <v>693.687</v>
+        <v>701.1460000000001</v>
       </c>
       <c r="G95">
         <v>141.9</v>
@@ -9077,45 +9077,45 @@
         <v>125.725</v>
       </c>
       <c r="M95">
-        <v>49.8760953</v>
+        <v>53.14686680000001</v>
       </c>
       <c r="N95">
-        <v>75.84890469999999</v>
+        <v>72.57813319999998</v>
       </c>
       <c r="O95">
-        <v>20.479204269</v>
+        <v>19.596095964</v>
       </c>
       <c r="P95">
-        <v>55.36970043099999</v>
+        <v>52.98203723599998</v>
       </c>
       <c r="Q95">
-        <v>78.26970043099999</v>
+        <v>75.88203723599999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6254266498884022</v>
+        <v>0.7195930838623494</v>
       </c>
       <c r="T95">
-        <v>10.61606564917762</v>
+        <v>12.34075695729612</v>
       </c>
       <c r="U95">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V95">
         <v>0.27</v>
       </c>
       <c r="W95">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.520746647141802</v>
+        <v>2.365614523865026</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09518954503174093</v>
+        <v>0.09513860457129374</v>
       </c>
       <c r="C96">
-        <v>-11.49546831732823</v>
+        <v>-18.38893419781755</v>
       </c>
       <c r="D96">
-        <v>547.7505316826719</v>
+        <v>548.3160658021825</v>
       </c>
       <c r="E96">
-        <v>276.6460000000001</v>
+        <v>284.105</v>
       </c>
       <c r="F96">
-        <v>701.1460000000001</v>
+        <v>708.605</v>
       </c>
       <c r="G96">
         <v>141.9</v>
@@ -9159,28 +9159,28 @@
         <v>125.725</v>
       </c>
       <c r="M96">
-        <v>53.14686680000001</v>
+        <v>53.712259</v>
       </c>
       <c r="N96">
-        <v>72.57813319999998</v>
+        <v>72.01274099999999</v>
       </c>
       <c r="O96">
-        <v>19.596095964</v>
+        <v>19.44344007</v>
       </c>
       <c r="P96">
-        <v>52.98203723599998</v>
+        <v>52.56930093</v>
       </c>
       <c r="Q96">
-        <v>75.88203723599999</v>
+        <v>75.46930093</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7195930838623494</v>
+        <v>0.8514260914258758</v>
       </c>
       <c r="T96">
-        <v>12.34075695729612</v>
+        <v>14.75532478866202</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.365614523865026</v>
+        <v>2.340713318350658</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09513860457129374</v>
+        <v>0.09508766411084653</v>
       </c>
       <c r="C97">
-        <v>-18.38893419781755</v>
+        <v>-25.28123108119701</v>
       </c>
       <c r="D97">
-        <v>548.3160658021825</v>
+        <v>548.8827689188031</v>
       </c>
       <c r="E97">
-        <v>284.105</v>
+        <v>291.5640000000001</v>
       </c>
       <c r="F97">
-        <v>708.605</v>
+        <v>716.0640000000001</v>
       </c>
       <c r="G97">
         <v>141.9</v>
@@ -9241,28 +9241,28 @@
         <v>125.725</v>
       </c>
       <c r="M97">
-        <v>53.712259</v>
+        <v>54.27765120000001</v>
       </c>
       <c r="N97">
-        <v>72.01274099999999</v>
+        <v>71.44734879999999</v>
       </c>
       <c r="O97">
-        <v>19.44344007</v>
+        <v>19.290784176</v>
       </c>
       <c r="P97">
-        <v>52.56930093</v>
+        <v>52.15656462399998</v>
       </c>
       <c r="Q97">
-        <v>75.46930093</v>
+        <v>75.05656462399999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8514260914258758</v>
+        <v>1.049175602771165</v>
       </c>
       <c r="T97">
-        <v>14.75532478866202</v>
+        <v>18.37717653571088</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.340713318350658</v>
+        <v>2.316330887951172</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09508766411084654</v>
+        <v>0.09503672365039934</v>
       </c>
       <c r="C98">
-        <v>-25.28123108119701</v>
+        <v>-32.17235533912299</v>
       </c>
       <c r="D98">
-        <v>548.882768918803</v>
+        <v>549.4506446608769</v>
       </c>
       <c r="E98">
-        <v>291.564</v>
+        <v>299.0229999999999</v>
       </c>
       <c r="F98">
-        <v>716.064</v>
+        <v>723.5229999999999</v>
       </c>
       <c r="G98">
         <v>141.9</v>
@@ -9323,28 +9323,28 @@
         <v>125.725</v>
       </c>
       <c r="M98">
-        <v>54.2776512</v>
+        <v>54.8430434</v>
       </c>
       <c r="N98">
-        <v>71.44734879999999</v>
+        <v>70.8819566</v>
       </c>
       <c r="O98">
-        <v>19.290784176</v>
+        <v>19.138128282</v>
       </c>
       <c r="P98">
-        <v>52.15656462399998</v>
+        <v>51.743828318</v>
       </c>
       <c r="Q98">
-        <v>75.05656462399999</v>
+        <v>74.643828318</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.049175602771163</v>
+        <v>1.378758121679977</v>
       </c>
       <c r="T98">
-        <v>18.37717653571083</v>
+        <v>24.41359611412557</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.316330887951172</v>
+        <v>2.292451188075387</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09503672365039934</v>
+        <v>0.09498578318995213</v>
       </c>
       <c r="C99">
-        <v>-32.17235533912299</v>
+        <v>-39.06230332822088</v>
       </c>
       <c r="D99">
-        <v>549.4506446608769</v>
+        <v>550.0196966717791</v>
       </c>
       <c r="E99">
-        <v>299.0229999999999</v>
+        <v>306.482</v>
       </c>
       <c r="F99">
-        <v>723.5229999999999</v>
+        <v>730.982</v>
       </c>
       <c r="G99">
         <v>141.9</v>
@@ -9405,28 +9405,28 @@
         <v>125.725</v>
       </c>
       <c r="M99">
-        <v>54.8430434</v>
+        <v>55.4084356</v>
       </c>
       <c r="N99">
-        <v>70.8819566</v>
+        <v>70.31656439999999</v>
       </c>
       <c r="O99">
-        <v>19.138128282</v>
+        <v>18.985472388</v>
       </c>
       <c r="P99">
-        <v>51.743828318</v>
+        <v>51.33109201199999</v>
       </c>
       <c r="Q99">
-        <v>74.643828318</v>
+        <v>74.231092012</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.378758121679977</v>
+        <v>2.037923159497605</v>
       </c>
       <c r="T99">
-        <v>24.41359611412557</v>
+        <v>36.48643527095503</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.292451188075387</v>
+        <v>2.269058829013393</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09498578318995213</v>
+        <v>0.09493484272950495</v>
       </c>
       <c r="C100">
-        <v>-39.06230332822088</v>
+        <v>-45.95107139000697</v>
       </c>
       <c r="D100">
-        <v>550.0196966717791</v>
+        <v>550.589928609993</v>
       </c>
       <c r="E100">
-        <v>306.482</v>
+        <v>313.9409999999999</v>
       </c>
       <c r="F100">
-        <v>730.982</v>
+        <v>738.4409999999999</v>
       </c>
       <c r="G100">
         <v>141.9</v>
@@ -9487,28 +9487,28 @@
         <v>125.725</v>
       </c>
       <c r="M100">
-        <v>55.4084356</v>
+        <v>55.9738278</v>
       </c>
       <c r="N100">
-        <v>70.31656439999999</v>
+        <v>69.7511722</v>
       </c>
       <c r="O100">
-        <v>18.985472388</v>
+        <v>18.832816494</v>
       </c>
       <c r="P100">
-        <v>51.33109201199999</v>
+        <v>50.918355706</v>
       </c>
       <c r="Q100">
-        <v>74.231092012</v>
+        <v>73.81835570600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.037923159497605</v>
+        <v>4.01541827295049</v>
       </c>
       <c r="T100">
-        <v>36.48643527095503</v>
+        <v>72.70495274144345</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.269058829013393</v>
+        <v>2.246139042861743</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09493484272950495</v>
-      </c>
-      <c r="C101">
-        <v>-45.95107139000697</v>
-      </c>
-      <c r="D101">
-        <v>550.589928609993</v>
-      </c>
-      <c r="E101">
-        <v>313.9409999999999</v>
-      </c>
-      <c r="F101">
-        <v>738.4409999999999</v>
-      </c>
-      <c r="G101">
-        <v>141.9</v>
-      </c>
-      <c r="H101">
-        <v>321.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>148.625</v>
-      </c>
-      <c r="K101">
-        <v>22.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>125.725</v>
-      </c>
-      <c r="M101">
-        <v>55.9738278</v>
-      </c>
-      <c r="N101">
-        <v>69.7511722</v>
-      </c>
-      <c r="O101">
-        <v>18.832816494</v>
-      </c>
-      <c r="P101">
-        <v>50.918355706</v>
-      </c>
-      <c r="Q101">
-        <v>73.81835570600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.01541827295049</v>
-      </c>
-      <c r="T101">
-        <v>72.70495274144345</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.055334</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.246139042861743</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
